--- a/Contenidos_Consultados/output/contenidos_consultados_detalle_enero_2026.xlsx
+++ b/Contenidos_Consultados/output/contenidos_consultados_detalle_enero_2026.xlsx
@@ -454,7 +454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E966"/>
+  <dimension ref="A1:E956"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B1" s="2" t="n">
-        <v>961</v>
+        <v>951</v>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
@@ -968,36 +968,36 @@
         </is>
       </c>
       <c r="B40" s="5" t="n">
-        <v>8397</v>
+        <v>8541</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>0.004020866174158046</v>
+        <v>0.004089819934915312</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TUR01CUX02 Apertura</t>
+          <t>SUA01CUX Pedido de mail obligatorio</t>
         </is>
       </c>
       <c r="B41" s="5" t="n">
-        <v>8357</v>
+        <v>8515</v>
       </c>
       <c r="C41" s="6" t="n">
-        <v>0.004001712351725472</v>
+        <v>0.004077369950334139</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SUA01CUX Pedido de mail obligatorio</t>
+          <t>TUR01CUX02 Apertura</t>
         </is>
       </c>
       <c r="B42" s="5" t="n">
-        <v>8343</v>
+        <v>8357</v>
       </c>
       <c r="C42" s="6" t="n">
-        <v>0.003995008513874071</v>
+        <v>0.004001712351725472</v>
       </c>
     </row>
     <row r="43">
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="B43" s="5" t="n">
-        <v>7887</v>
+        <v>8023</v>
       </c>
       <c r="C43" s="6" t="n">
-        <v>0.003776654938142731</v>
+        <v>0.003841777934413481</v>
       </c>
     </row>
     <row r="44">
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="B44" s="5" t="n">
-        <v>7601</v>
+        <v>7706</v>
       </c>
       <c r="C44" s="6" t="n">
-        <v>0.003639705107749828</v>
+        <v>0.003689983891635334</v>
       </c>
     </row>
     <row r="45">
@@ -1527,10 +1527,10 @@
         </is>
       </c>
       <c r="B83" s="5" t="n">
-        <v>2854</v>
+        <v>2877</v>
       </c>
       <c r="C83" s="6" t="n">
-        <v>0.001366625230564137</v>
+        <v>0.001377638678462868</v>
       </c>
     </row>
     <row r="84">
@@ -1848,27 +1848,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MO03CUX01 Otros abonos y pases</t>
+          <t>MO05CUX10 Apertura de contingencia</t>
         </is>
       </c>
       <c r="B108" s="5" t="n">
-        <v>1805</v>
+        <v>1784</v>
       </c>
       <c r="C108" s="6" t="n">
-        <v>0.0008643162372698908</v>
+        <v>0.0008542604804927896</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MO05CUX10 Apertura de contingencia</t>
+          <t>MO03CUX01 Otros abonos y pases</t>
         </is>
       </c>
       <c r="B109" s="5" t="n">
-        <v>1784</v>
+        <v>1766</v>
       </c>
       <c r="C109" s="6" t="n">
-        <v>0.0008542604804927896</v>
+        <v>0.0008456412603981314</v>
       </c>
     </row>
     <row r="110">
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="B122" s="5" t="n">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="C122" s="6" t="n">
-        <v>0.0007039029743970855</v>
+        <v>0.0007043818199578999</v>
       </c>
     </row>
     <row r="123">
@@ -2329,40 +2329,40 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Flow fulfilled of "Primera vez"</t>
+          <t>MO11CUX01 Apertura</t>
         </is>
       </c>
       <c r="B145" s="5" t="n">
-        <v>1102</v>
+        <v>1107</v>
       </c>
       <c r="C145" s="6" t="n">
-        <v>0.000527687808017407</v>
+        <v>0.0005300820358214787</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>DE02CUX01 Apertura</t>
+          <t>Flow fulfilled of "Primera vez"</t>
         </is>
       </c>
       <c r="B146" s="5" t="n">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="C146" s="6" t="n">
-        <v>0.000526251271334964</v>
+        <v>0.000527687808017407</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>MO11CUX01 Apertura</t>
+          <t>DE02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B147" s="5" t="n">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="C147" s="6" t="n">
-        <v>0.0005257724257741496</v>
+        <v>0.000526251271334964</v>
       </c>
     </row>
     <row r="148">
@@ -2433,7 +2433,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>¿Cómo lo declaro mi domicilio?</t>
+          <t>TR04CUX11 Apertura</t>
         </is>
       </c>
       <c r="B153" s="5" t="n">
@@ -2446,7 +2446,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>TR04CUX11 Apertura</t>
+          <t>¿Cómo lo declaro mi domicilio?</t>
         </is>
       </c>
       <c r="B154" s="5" t="n">
@@ -2472,157 +2472,157 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MO04CUX01 Hacer la VTV</t>
+          <t>SE01CUX03 Apertura</t>
         </is>
       </c>
       <c r="B156" s="5" t="n">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="C156" s="6" t="n">
-        <v>0.0004932109276387743</v>
+        <v>0.0004922532365171455</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SE01CUX03 Apertura</t>
+          <t>RC01CUX06 Apertura</t>
         </is>
       </c>
       <c r="B157" s="5" t="n">
-        <v>1028</v>
+        <v>1008</v>
       </c>
       <c r="C157" s="6" t="n">
-        <v>0.0004922532365171455</v>
+        <v>0.0004826763253008586</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>RC01CUX06 Apertura</t>
+          <t>SUA01CUX08 Apertura</t>
         </is>
       </c>
       <c r="B158" s="5" t="n">
-        <v>1008</v>
+        <v>999</v>
       </c>
       <c r="C158" s="6" t="n">
-        <v>0.0004826763253008586</v>
+        <v>0.0004783667152535296</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SUA01CUX08 Apertura</t>
+          <t>CU00CUX01 Super Apertura</t>
         </is>
       </c>
       <c r="B159" s="5" t="n">
-        <v>999</v>
+        <v>990</v>
       </c>
       <c r="C159" s="6" t="n">
-        <v>0.0004783667152535296</v>
+        <v>0.0004740571052062005</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>CU00CUX01 Super Apertura</t>
+          <t>DEC02CUX02 Apertura</t>
         </is>
       </c>
       <c r="B160" s="5" t="n">
-        <v>990</v>
+        <v>981</v>
       </c>
       <c r="C160" s="6" t="n">
-        <v>0.0004740571052062005</v>
+        <v>0.0004697474951588714</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>DEC02CUX02 Apertura</t>
+          <t>DH10CUX01 Apertura</t>
         </is>
       </c>
       <c r="B161" s="5" t="n">
-        <v>981</v>
+        <v>963</v>
       </c>
       <c r="C161" s="6" t="n">
-        <v>0.0004697474951588714</v>
+        <v>0.0004611282750642132</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>DH10CUX01 Apertura</t>
+          <t>TRA04CUX01 Apertura</t>
         </is>
       </c>
       <c r="B162" s="5" t="n">
-        <v>963</v>
+        <v>951</v>
       </c>
       <c r="C162" s="6" t="n">
-        <v>0.0004611282750642132</v>
+        <v>0.0004553821283344411</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TRA04CUX01 Apertura</t>
+          <t>No Encontró Ubicación Permitido Estacionar</t>
         </is>
       </c>
       <c r="B163" s="5" t="n">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="C163" s="6" t="n">
-        <v>0.0004553821283344411</v>
+        <v>0.0004549032827736267</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>No Encontró Ubicación Permitido Estacionar</t>
+          <t>MO04CUX03 Apertura</t>
         </is>
       </c>
       <c r="B164" s="5" t="n">
-        <v>950</v>
+        <v>939</v>
       </c>
       <c r="C164" s="6" t="n">
-        <v>0.0004549032827736267</v>
+        <v>0.000449635981604669</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MO04CUX03 Apertura</t>
+          <t>Error general acciones de código</t>
         </is>
       </c>
       <c r="B165" s="5" t="n">
-        <v>939</v>
+        <v>918</v>
       </c>
       <c r="C165" s="6" t="n">
-        <v>0.000449635981604669</v>
+        <v>0.0004395802248275677</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Error general acciones de código</t>
+          <t>DDHH03CUX07 Apertura</t>
         </is>
       </c>
       <c r="B166" s="5" t="n">
-        <v>938</v>
+        <v>897</v>
       </c>
       <c r="C166" s="6" t="n">
-        <v>0.0004491571360438546</v>
+        <v>0.0004295244680504665</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>DDHH03CUX07 Apertura</t>
+          <t>MO04CUX01 Hacer la VTV</t>
         </is>
       </c>
       <c r="B167" s="5" t="n">
-        <v>897</v>
+        <v>894</v>
       </c>
       <c r="C167" s="6" t="n">
-        <v>0.0004295244680504665</v>
+        <v>0.0004280879313680235</v>
       </c>
     </row>
     <row r="168">
@@ -2784,27 +2784,27 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>AGC02CUX01 Apertura</t>
+          <t>MO03CUX01 Apertura</t>
         </is>
       </c>
       <c r="B180" s="5" t="n">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C180" s="6" t="n">
-        <v>0.0003806822208474034</v>
+        <v>0.0003811610664082178</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SUA01CUX11 Apertura</t>
+          <t>AGC02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B181" s="5" t="n">
-        <v>786</v>
+        <v>795</v>
       </c>
       <c r="C181" s="6" t="n">
-        <v>0.0003763726108000743</v>
+        <v>0.0003806822208474034</v>
       </c>
     </row>
     <row r="182">
@@ -2823,118 +2823,118 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>EDU05CUX06 Apertura</t>
+          <t>SUA01CUX11 Apertura</t>
         </is>
       </c>
       <c r="B183" s="5" t="n">
-        <v>780</v>
+        <v>786</v>
       </c>
       <c r="C183" s="6" t="n">
-        <v>0.0003734995374351883</v>
+        <v>0.0003763726108000743</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>EM03CUX01 Apertura</t>
+          <t>EDU05CUX06 Apertura</t>
         </is>
       </c>
       <c r="B184" s="5" t="n">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C184" s="6" t="n">
-        <v>0.0003730206918743739</v>
+        <v>0.0003734995374351883</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>CU01CUX06 Apertura</t>
+          <t>EM03CUX01 Apertura</t>
         </is>
       </c>
       <c r="B185" s="5" t="n">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C185" s="6" t="n">
-        <v>0.0003720630007527452</v>
+        <v>0.0003730206918743739</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ED00CUX01 Cursos</t>
+          <t>CU01CUX06 Apertura</t>
         </is>
       </c>
       <c r="B186" s="5" t="n">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C186" s="6" t="n">
-        <v>0.0003706264640703022</v>
+        <v>0.0003720630007527452</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>GE01CUX02 Apertura</t>
+          <t>ED00CUX01 Cursos</t>
         </is>
       </c>
       <c r="B187" s="5" t="n">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="C187" s="6" t="n">
-        <v>0.0003687110818270448</v>
+        <v>0.0003706264640703022</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>¿Qué necesito para declarar domicilio?</t>
+          <t>GE01CUX02 Apertura</t>
         </is>
       </c>
       <c r="B188" s="5" t="n">
-        <v>765</v>
+        <v>770</v>
       </c>
       <c r="C188" s="6" t="n">
-        <v>0.0003663168540229731</v>
+        <v>0.0003687110818270448</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>AC02CUX04 Teléfonos Emergencias</t>
+          <t>¿Qué necesito para declarar domicilio?</t>
         </is>
       </c>
       <c r="B189" s="5" t="n">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="C189" s="6" t="n">
-        <v>0.0003644014717797157</v>
+        <v>0.0003663168540229731</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>VI00CUX01 Apertura</t>
+          <t>AC02CUX04 Teléfonos Emergencias</t>
         </is>
       </c>
       <c r="B190" s="5" t="n">
-        <v>760</v>
+        <v>765</v>
       </c>
       <c r="C190" s="6" t="n">
-        <v>0.0003639226262189014</v>
+        <v>0.0003663168540229731</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>MO03CUX01 Apertura</t>
+          <t>VI00CUX01 Apertura</t>
         </is>
       </c>
       <c r="B191" s="5" t="n">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="C191" s="6" t="n">
-        <v>0.0003624860895364584</v>
+        <v>0.0003639226262189014</v>
       </c>
     </row>
     <row r="192">
@@ -3009,10 +3009,10 @@
         </is>
       </c>
       <c r="B197" s="5" t="n">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C197" s="6" t="n">
-        <v>0.0003347130470092264</v>
+        <v>0.0003332765103267834</v>
       </c>
     </row>
     <row r="198">
@@ -3022,10 +3022,10 @@
         </is>
       </c>
       <c r="B198" s="5" t="n">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C198" s="6" t="n">
-        <v>0.000334234201448412</v>
+        <v>0.000332797664765969</v>
       </c>
     </row>
     <row r="199">
@@ -3096,27 +3096,27 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>MO08CUX01 Apertura</t>
+          <t>SA07CUX01 Hepatitis B</t>
         </is>
       </c>
       <c r="B204" s="5" t="n">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C204" s="6" t="n">
-        <v>0.0003059823133603658</v>
+        <v>0.0003064611589211801</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>CU09CUX01 CCK</t>
+          <t>MO08CUX01 Apertura</t>
         </is>
       </c>
       <c r="B205" s="5" t="n">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="C205" s="6" t="n">
-        <v>0.000302151548873851</v>
+        <v>0.0003059823133603658</v>
       </c>
     </row>
     <row r="206">
@@ -3148,7 +3148,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SE07CUX01 Policía</t>
+          <t>CU09CUX01 CCK</t>
         </is>
       </c>
       <c r="B208" s="5" t="n">
@@ -3161,228 +3161,228 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>IN01CUX03 Apertura Vehículo</t>
+          <t>SE07CUX01 Policía</t>
         </is>
       </c>
       <c r="B209" s="5" t="n">
-        <v>617</v>
+        <v>623</v>
       </c>
       <c r="C209" s="6" t="n">
-        <v>0.0002954477110224502</v>
+        <v>0.0002983207843873363</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>BX01CUX01 Apertura</t>
+          <t>IN01CUX03 Apertura Vehículo</t>
         </is>
       </c>
       <c r="B210" s="5" t="n">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="C210" s="6" t="n">
-        <v>0.0002920957920967498</v>
+        <v>0.0002954477110224502</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>MO01CUX01 Apertura</t>
+          <t>BX01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B211" s="5" t="n">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C211" s="6" t="n">
-        <v>0.0002901804098534924</v>
+        <v>0.0002920957920967498</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>DH07CUX02 SAP Inclusión Laboral</t>
+          <t>MO01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B212" s="5" t="n">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C212" s="6" t="n">
-        <v>0.0002892227187318637</v>
+        <v>0.0002901804098534924</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TR04CUX24 Apertura</t>
+          <t>DH07CUX02 SAP Inclusión Laboral</t>
         </is>
       </c>
       <c r="B213" s="5" t="n">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="C213" s="6" t="n">
-        <v>0.0002877861820494207</v>
+        <v>0.0002892227187318637</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Test IABA</t>
+          <t>CIU05CUX09 Apertura</t>
         </is>
       </c>
       <c r="B214" s="5" t="n">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C214" s="6" t="n">
-        <v>0.000286828490927792</v>
+        <v>0.0002887438731710494</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>CIU02CUX01 Apertura</t>
+          <t>TR04CUX24 Apertura</t>
         </is>
       </c>
       <c r="B215" s="5" t="n">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C215" s="6" t="n">
-        <v>0.0002863496453669777</v>
+        <v>0.0002877861820494207</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TR03CUX28 Trámites por venta de vehículo ante la Dirección Nacional de los Registros Nacionales de la Propiedad del Automotor y Créditos Prendarios</t>
+          <t>Test IABA</t>
         </is>
       </c>
       <c r="B216" s="5" t="n">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="C216" s="6" t="n">
-        <v>0.0002839554175629059</v>
+        <v>0.000286828490927792</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>EDU01CUX00 Superapertura Becas</t>
+          <t>CIU02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B217" s="5" t="n">
-        <v>579</v>
+        <v>598</v>
       </c>
       <c r="C217" s="6" t="n">
-        <v>0.0002772515797115052</v>
+        <v>0.0002863496453669777</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CIU05CUX09 Apertura</t>
+          <t>TR03CUX28 Trámites por venta de vehículo ante la Dirección Nacional de los Registros Nacionales de la Propiedad del Automotor y Créditos Prendarios</t>
         </is>
       </c>
       <c r="B218" s="5" t="n">
-        <v>569</v>
+        <v>593</v>
       </c>
       <c r="C218" s="6" t="n">
-        <v>0.0002724631241033617</v>
+        <v>0.0002839554175629059</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>DH08CUX01 Apertura</t>
+          <t>EDU01CUX00 Superapertura Becas</t>
         </is>
       </c>
       <c r="B219" s="5" t="n">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="C219" s="6" t="n">
-        <v>0.0002719842785425473</v>
+        <v>0.0002772515797115052</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CO12CUX03 Servicios de feriado</t>
+          <t>DH08CUX01 Apertura</t>
         </is>
       </c>
       <c r="B220" s="5" t="n">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C220" s="6" t="n">
-        <v>0.000271505432981733</v>
+        <v>0.0002719842785425473</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>MO05CUX12 Apertura</t>
+          <t>CO12CUX03 Servicios de feriado</t>
         </is>
       </c>
       <c r="B221" s="5" t="n">
-        <v>542</v>
+        <v>567</v>
       </c>
       <c r="C221" s="6" t="n">
-        <v>0.0002595342939613744</v>
+        <v>0.000271505432981733</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>CIU06CUX01 Apertura</t>
+          <t>MO05CUX12 Apertura</t>
         </is>
       </c>
       <c r="B222" s="5" t="n">
-        <v>540</v>
+        <v>548</v>
       </c>
       <c r="C222" s="6" t="n">
-        <v>0.0002585766028397457</v>
+        <v>0.0002624073673262605</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TUR01CUX05 Pago de BUI</t>
+          <t>CIU06CUX01 Apertura</t>
         </is>
       </c>
       <c r="B223" s="5" t="n">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C223" s="6" t="n">
-        <v>0.0002580977572789314</v>
+        <v>0.0002585766028397457</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>SA07CUX01 Hepatitis B</t>
+          <t>DEC02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B224" s="5" t="n">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="C224" s="6" t="n">
-        <v>0.000257618911718117</v>
+        <v>0.0002533093016707879</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>DEC02CUX01 Apertura</t>
+          <t>DEC05CUX01 Apertura</t>
         </is>
       </c>
       <c r="B225" s="5" t="n">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="C225" s="6" t="n">
-        <v>0.0002533093016707879</v>
+        <v>0.0002470843093802015</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>DEC05CUX01 Apertura</t>
+          <t>TUR01CUX05 Pago de BUI</t>
         </is>
       </c>
       <c r="B226" s="5" t="n">
@@ -3395,7 +3395,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>TR03CUX31 Apertura</t>
+          <t>EDU05CUX04 Apertura</t>
         </is>
       </c>
       <c r="B227" s="5" t="n">
@@ -3408,7 +3408,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>EDU05CUX04 Apertura</t>
+          <t>TR03CUX31 Apertura</t>
         </is>
       </c>
       <c r="B228" s="5" t="n">
@@ -3473,46 +3473,46 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>TR04CUX41 Antecedentes penales</t>
+          <t>Consulta de Expedientes Electrónicos *Apertura</t>
         </is>
       </c>
       <c r="B233" s="5" t="n">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C233" s="6" t="n">
-        <v>0.0002394227804071719</v>
+        <v>0.0002379862437247289</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Consulta de Expedientes Electrónicos *Apertura</t>
+          <t>Tagear UsuarioPrueba</t>
         </is>
       </c>
       <c r="B234" s="5" t="n">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="C234" s="6" t="n">
-        <v>0.0002379862437247289</v>
+        <v>0.0002351131703598429</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Tagear UsuarioPrueba</t>
+          <t>EDU04CUX26 Apertura web</t>
         </is>
       </c>
       <c r="B235" s="5" t="n">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C235" s="6" t="n">
-        <v>0.0002351131703598429</v>
+        <v>0.0002341554792382142</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>EDU04CUX26 Apertura web</t>
+          <t>TR04CUX41 Antecedentes penales</t>
         </is>
       </c>
       <c r="B236" s="5" t="n">
@@ -3525,92 +3525,92 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>CU08CUX06 Atardeceres</t>
+          <t>DH09CUX02 Apertura</t>
         </is>
       </c>
       <c r="B237" s="5" t="n">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C237" s="6" t="n">
-        <v>0.0002303247147516994</v>
+        <v>0.0002279304869476277</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>DH09CUX02 Apertura</t>
+          <t>COY08CUX01 Apertura</t>
         </is>
       </c>
       <c r="B238" s="5" t="n">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C238" s="6" t="n">
-        <v>0.0002279304869476277</v>
+        <v>0.0002274516413868134</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>COY08CUX01 Apertura</t>
+          <t>SUA01CUX34 Vaciado de contenedor</t>
         </is>
       </c>
       <c r="B239" s="5" t="n">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C239" s="6" t="n">
-        <v>0.0002274516413868134</v>
+        <v>0.000226972795825999</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>SUA01CUX34 Vaciado de contenedor</t>
+          <t>CU08CUX06 Verano Joven BA</t>
         </is>
       </c>
       <c r="B240" s="5" t="n">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C240" s="6" t="n">
-        <v>0.0002274516413868134</v>
+        <v>0.0002264939502651847</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>CU08CUX06 Verano Joven BA</t>
+          <t>VI01CUX03 Apertura</t>
         </is>
       </c>
       <c r="B241" s="5" t="n">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C241" s="6" t="n">
-        <v>0.0002264939502651847</v>
+        <v>0.0002260151047043703</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>VI01CUX03 Apertura</t>
+          <t>TR03CUX17 Tarjeta control</t>
         </is>
       </c>
       <c r="B242" s="5" t="n">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="C242" s="6" t="n">
-        <v>0.0002264939502651847</v>
+        <v>0.0002245785680219273</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>TR03CUX17 Tarjeta control</t>
+          <t>CU08CUX06 Atardeceres</t>
         </is>
       </c>
       <c r="B243" s="5" t="n">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C243" s="6" t="n">
-        <v>0.0002245785680219273</v>
+        <v>0.0002221843402178556</v>
       </c>
     </row>
     <row r="244">
@@ -3629,7 +3629,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>SUA01CUX25 Apertura</t>
+          <t xml:space="preserve"> SA17CUX01 Por ahora no</t>
         </is>
       </c>
       <c r="B245" s="5" t="n">
@@ -3642,7 +3642,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SA17CUX01 Por ahora no</t>
+          <t>SUA01CUX25 Apertura</t>
         </is>
       </c>
       <c r="B246" s="5" t="n">
@@ -3668,98 +3668,98 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>CU02CUX02 Apertura</t>
+          <t>Error Permitido Estacionar</t>
         </is>
       </c>
       <c r="B248" s="5" t="n">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C248" s="6" t="n">
-        <v>0.0002169170390488978</v>
+        <v>0.0002173958846097121</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>MO01CUX02 Apertura</t>
+          <t>CU02CUX02 Apertura</t>
         </is>
       </c>
       <c r="B249" s="5" t="n">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C249" s="6" t="n">
-        <v>0.0002150016568056404</v>
+        <v>0.0002169170390488978</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>CU05CUX01 Apertura</t>
+          <t>MO01CUX02 Apertura</t>
         </is>
       </c>
       <c r="B250" s="5" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="C250" s="6" t="n">
-        <v>0.0002140439656840117</v>
+        <v>0.0002150016568056404</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>TR02CUX12 Cómo es el trámite</t>
+          <t>SE02CUX01 Cómo evitar estafas</t>
         </is>
       </c>
       <c r="B251" s="5" t="n">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C251" s="6" t="n">
-        <v>0.0002135651201231974</v>
+        <v>0.0002140439656840117</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>VI01CUX05 Apertura</t>
+          <t>CU05CUX01 Apertura</t>
         </is>
       </c>
       <c r="B252" s="5" t="n">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="C252" s="6" t="n">
-        <v>0.0002130862745623831</v>
+        <v>0.0002140439656840117</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>EDU01CUX01 Apertura</t>
+          <t>VI01CUX05 Apertura</t>
         </is>
       </c>
       <c r="B253" s="5" t="n">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C253" s="6" t="n">
-        <v>0.0002126074290015687</v>
+        <v>0.0002130862745623831</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>SE02CUX01 Cómo evitar estafas</t>
+          <t>EDU01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B254" s="5" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C254" s="6" t="n">
-        <v>0.0002111708923191257</v>
+        <v>0.0002126074290015687</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>EP05CUX02 Apertura</t>
+          <t>TR02CUX12 Cómo es el trámite</t>
         </is>
       </c>
       <c r="B255" s="5" t="n">
@@ -3772,14 +3772,14 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>EDU04CUX25 Apertura</t>
+          <t>EP05CUX02 Apertura</t>
         </is>
       </c>
       <c r="B256" s="5" t="n">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C256" s="6" t="n">
-        <v>0.0002106920467583113</v>
+        <v>0.0002111708923191257</v>
       </c>
     </row>
     <row r="257">
@@ -3798,7 +3798,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TR03CUX17 Permiso de carga excepcional (por viaje)</t>
+          <t>EDU04CUX25 Apertura</t>
         </is>
       </c>
       <c r="B258" s="5" t="n">
@@ -3811,46 +3811,46 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Error Permitido Estacionar</t>
+          <t>TR03CUX17 Permiso de carga excepcional (por viaje)</t>
         </is>
       </c>
       <c r="B259" s="5" t="n">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C259" s="6" t="n">
-        <v>0.0002078189733934253</v>
+        <v>0.0002097343556366826</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>MO06CUX02 Apertura</t>
+          <t>VI01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B260" s="5" t="n">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C260" s="6" t="n">
-        <v>0.0002078189733934253</v>
+        <v>0.0002082978189542396</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>VI01CUX01 Apertura</t>
+          <t>MO06CUX02 Apertura</t>
         </is>
       </c>
       <c r="B261" s="5" t="n">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C261" s="6" t="n">
-        <v>0.0002073401278326109</v>
+        <v>0.0002078189733934253</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>AGC01CUX01  Apertura</t>
+          <t>DDHH03CUX08 Apertura</t>
         </is>
       </c>
       <c r="B262" s="5" t="n">
@@ -3863,7 +3863,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>DDHH03CUX08 Apertura</t>
+          <t>AGC01CUX01  Apertura</t>
         </is>
       </c>
       <c r="B263" s="5" t="n">
@@ -3919,10 +3919,10 @@
         </is>
       </c>
       <c r="B267" s="5" t="n">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C267" s="6" t="n">
-        <v>0.0001968055254946953</v>
+        <v>0.0001972843710555097</v>
       </c>
     </row>
     <row r="268">
@@ -3971,10 +3971,10 @@
         </is>
       </c>
       <c r="B271" s="5" t="n">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C271" s="6" t="n">
-        <v>0.0001848343864743368</v>
+        <v>0.0001862709231567798</v>
       </c>
     </row>
     <row r="272">
@@ -4058,7 +4058,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>CU08CUX06 BA Afters</t>
+          <t>EDU01CUX02 Apertura</t>
         </is>
       </c>
       <c r="B278" s="5" t="n">
@@ -4071,14 +4071,14 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>EDU01CUX02 Apertura</t>
+          <t>CU08CUX06 BA Afters</t>
         </is>
       </c>
       <c r="B279" s="5" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C279" s="6" t="n">
-        <v>0.0001695113285282778</v>
+        <v>0.0001709478652107208</v>
       </c>
     </row>
     <row r="280">
@@ -4097,7 +4097,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>TR04CUX32  Primer pasaporte</t>
+          <t>TR03CUX03 Proescritores</t>
         </is>
       </c>
       <c r="B281" s="5" t="n">
@@ -4110,27 +4110,27 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>SA14CUX01 Apertura</t>
+          <t>TR04CUX32  Primer pasaporte</t>
         </is>
       </c>
       <c r="B282" s="5" t="n">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C282" s="6" t="n">
-        <v>0.000165680564041763</v>
+        <v>0.000167117100724206</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>TR01CUX11 Apertura</t>
+          <t>SA14CUX01 Apertura</t>
         </is>
       </c>
       <c r="B283" s="5" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C283" s="6" t="n">
-        <v>0.0001652017184809486</v>
+        <v>0.000165680564041763</v>
       </c>
     </row>
     <row r="284">
@@ -4149,33 +4149,33 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>TR03CUX03 Proescritores</t>
+          <t>TR01CUX11 Apertura</t>
         </is>
       </c>
       <c r="B285" s="5" t="n">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C285" s="6" t="n">
-        <v>0.0001647228729201343</v>
+        <v>0.0001652017184809486</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>SA07CUX01 Anticonceptivos</t>
+          <t>BA Empresas</t>
         </is>
       </c>
       <c r="B286" s="5" t="n">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C286" s="6" t="n">
-        <v>0.0001647228729201343</v>
+        <v>0.0001637651817985056</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>TR04CUX32  Apertura</t>
+          <t>EM01CUX02 Apertura</t>
         </is>
       </c>
       <c r="B287" s="5" t="n">
@@ -4188,7 +4188,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>EM01CUX02 Apertura</t>
+          <t>TR04CUX32  Apertura</t>
         </is>
       </c>
       <c r="B288" s="5" t="n">
@@ -4201,7 +4201,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>JU01CUX01 Apertura</t>
+          <t>SUA01CUX29 Apertura columnas en mal estado</t>
         </is>
       </c>
       <c r="B289" s="5" t="n">
@@ -4214,7 +4214,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>AGC02CUX02 Director de Obra</t>
+          <t>JU01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B290" s="5" t="n">
@@ -4227,7 +4227,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>SUA01CUX29 Apertura columnas en mal estado</t>
+          <t>AGC02CUX02 Director de Obra</t>
         </is>
       </c>
       <c r="B291" s="5" t="n">
@@ -4240,33 +4240,33 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>BA Empresas</t>
+          <t>TUR02CUX01 - No hay turnos disponibles</t>
         </is>
       </c>
       <c r="B292" s="5" t="n">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C292" s="6" t="n">
-        <v>0.0001618497995552483</v>
+        <v>0.0001608921084336195</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>TUR02CUX01 - No hay turnos disponibles</t>
+          <t>CO10CUX02 Apertura post evento</t>
         </is>
       </c>
       <c r="B293" s="5" t="n">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="C293" s="6" t="n">
-        <v>0.0001608921084336195</v>
+        <v>0.0001570613439471048</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>CO10CUX02 Apertura post evento</t>
+          <t>CU04CUX40 Apertura post evento</t>
         </is>
       </c>
       <c r="B294" s="5" t="n">
@@ -4279,183 +4279,183 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>CU04CUX40 Apertura post evento</t>
+          <t>DE05CUX05 Apertura</t>
         </is>
       </c>
       <c r="B295" s="5" t="n">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C295" s="6" t="n">
-        <v>0.0001570613439471048</v>
+        <v>0.0001561036528254761</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>DE05CUX05 Apertura</t>
+          <t>SA02CUX01 Evaluación COVID-19</t>
         </is>
       </c>
       <c r="B296" s="5" t="n">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C296" s="6" t="n">
-        <v>0.0001561036528254761</v>
+        <v>0.0001556248072646618</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>SA02CUX01 Evaluación COVID-19</t>
+          <t>SUA01CUX34 Lavado de contenedor</t>
         </is>
       </c>
       <c r="B297" s="5" t="n">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="C297" s="6" t="n">
-        <v>0.0001556248072646618</v>
+        <v>0.0001527517338997757</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>SUA01CUX34 Lavado de contenedor</t>
+          <t>AM02CUX03 Apertura</t>
         </is>
       </c>
       <c r="B298" s="5" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C298" s="6" t="n">
-        <v>0.0001522728883389614</v>
+        <v>0.000151794042778147</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>AM02CUX03 Apertura</t>
+          <t>EDU01CUX03 Apertura</t>
         </is>
       </c>
       <c r="B299" s="5" t="n">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C299" s="6" t="n">
-        <v>0.000151794042778147</v>
+        <v>0.0001513151972173327</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>EDU01CUX03 Apertura</t>
+          <t>EDU03CUX05  Apertura</t>
         </is>
       </c>
       <c r="B300" s="5" t="n">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C300" s="6" t="n">
-        <v>0.0001513151972173327</v>
+        <v>0.0001493998149740753</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>EDU03CUX05  Apertura</t>
+          <t>Resultado hisopado no encontrado</t>
         </is>
       </c>
       <c r="B301" s="5" t="n">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="C301" s="6" t="n">
-        <v>0.0001493998149740753</v>
+        <v>0.0001484421238524466</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Resultado hisopado no encontrado</t>
+          <t>DH11CUX01 Más cursos</t>
         </is>
       </c>
       <c r="B302" s="5" t="n">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C302" s="6" t="n">
-        <v>0.0001484421238524466</v>
+        <v>0.0001474844327308179</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>DH11CUX01 Más cursos</t>
+          <t>SUA01CUX13 Apertura</t>
         </is>
       </c>
       <c r="B303" s="5" t="n">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C303" s="6" t="n">
-        <v>0.0001474844327308179</v>
+        <v>0.0001455690504875605</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>SUA01CUX13 Apertura</t>
+          <t>INN10CUX13 - Vuelta</t>
         </is>
       </c>
       <c r="B304" s="5" t="n">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C304" s="6" t="n">
-        <v>0.0001455690504875605</v>
+        <v>0.0001450902049267462</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>INN10CUX13 - Vuelta</t>
+          <t>ED04CUX15 Apertura</t>
         </is>
       </c>
       <c r="B305" s="5" t="n">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C305" s="6" t="n">
-        <v>0.0001450902049267462</v>
+        <v>0.0001446113593659319</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ED04CUX15 Apertura</t>
+          <t>¿Como estás?</t>
         </is>
       </c>
       <c r="B306" s="5" t="n">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="C306" s="6" t="n">
-        <v>0.0001446113593659319</v>
+        <v>0.0001436536682443032</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>¿Como estás?</t>
+          <t>SA10CUX03 Mapa de Salud</t>
         </is>
       </c>
       <c r="B307" s="5" t="n">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="C307" s="6" t="n">
-        <v>0.0001436536682443032</v>
+        <v>0.0001426959771226745</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>SA10CUX03 Mapa de Salud</t>
+          <t>DH03CUX03 Apertura</t>
         </is>
       </c>
       <c r="B308" s="5" t="n">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C308" s="6" t="n">
-        <v>0.0001426959771226745</v>
+        <v>0.0001412594404402315</v>
       </c>
     </row>
     <row r="309">
@@ -4500,14 +4500,14 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>DH03CUX03 Apertura</t>
+          <t>DH04CUX05 Apertura</t>
         </is>
       </c>
       <c r="B312" s="5" t="n">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C312" s="6" t="n">
-        <v>0.0001398229037577884</v>
+        <v>0.0001388652126361597</v>
       </c>
     </row>
     <row r="313">
@@ -4526,14 +4526,14 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>DH04CUX05 Apertura</t>
+          <t>TR03CUX22 Apertura</t>
         </is>
       </c>
       <c r="B314" s="5" t="n">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="C314" s="6" t="n">
-        <v>0.000137907521514531</v>
+        <v>0.0001316825292239446</v>
       </c>
     </row>
     <row r="315">
@@ -4543,23 +4543,23 @@
         </is>
       </c>
       <c r="B315" s="5" t="n">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C315" s="6" t="n">
-        <v>0.0001326402203455733</v>
+        <v>0.0001316825292239446</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>TR03CUX22 Apertura</t>
+          <t>TR02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B316" s="5" t="n">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C316" s="6" t="n">
-        <v>0.0001316825292239446</v>
+        <v>0.0001302459925415015</v>
       </c>
     </row>
     <row r="317">
@@ -4591,7 +4591,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>GA04CUX17 Apertura</t>
+          <t>Número de Documento Inválido | Estado de Trámites</t>
         </is>
       </c>
       <c r="B319" s="5" t="n">
@@ -4604,7 +4604,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Número de Documento Inválido | Estado de Trámites</t>
+          <t>GA04CUX17 Apertura</t>
         </is>
       </c>
       <c r="B320" s="5" t="n">
@@ -4617,40 +4617,40 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>TR02CUX01 Apertura</t>
+          <t>TR03CUX20 Apertura</t>
         </is>
       </c>
       <c r="B321" s="5" t="n">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="C321" s="6" t="n">
-        <v>0.0001273729191766155</v>
+        <v>0.0001264152280549868</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>TR03CUX20 Apertura</t>
+          <t>TU04CUX02 Preapertura</t>
         </is>
       </c>
       <c r="B322" s="5" t="n">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="C322" s="6" t="n">
-        <v>0.0001264152280549868</v>
+        <v>0.0001254575369333581</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>TU04CUX02 Preapertura</t>
+          <t>SUA01CUX36 Reparación de semaforo</t>
         </is>
       </c>
       <c r="B323" s="5" t="n">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C323" s="6" t="n">
-        <v>0.0001254575369333581</v>
+        <v>0.0001230633091292864</v>
       </c>
     </row>
     <row r="324">
@@ -4660,172 +4660,172 @@
         </is>
       </c>
       <c r="B324" s="5" t="n">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C324" s="6" t="n">
-        <v>0.0001240210002509151</v>
+        <v>0.000122584463568472</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>SUA01CUX36 Reparación de semaforo</t>
+          <t>VI01CUX07 Apertura</t>
         </is>
       </c>
       <c r="B325" s="5" t="n">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C325" s="6" t="n">
-        <v>0.0001230633091292864</v>
+        <v>0.000121147926886029</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>VI01CUX07 Apertura</t>
+          <t xml:space="preserve">GA03CUX15 Apertura </t>
         </is>
       </c>
       <c r="B326" s="5" t="n">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C326" s="6" t="n">
-        <v>0.000121147926886029</v>
+        <v>0.0001201902357644003</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t xml:space="preserve">GA03CUX15 Apertura </t>
+          <t>CU11CUX02 Apertura</t>
         </is>
       </c>
       <c r="B327" s="5" t="n">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C327" s="6" t="n">
-        <v>0.0001201902357644003</v>
+        <v>0.0001192325446427716</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>EP05CUX01 Apertura</t>
+          <t xml:space="preserve">EDU07CUX01  Apertura </t>
         </is>
       </c>
       <c r="B328" s="5" t="n">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C328" s="6" t="n">
-        <v>0.0001192325446427716</v>
+        <v>0.0001187536990819573</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>SE02CUX01 Apertura</t>
+          <t>EP05CUX01 Apertura</t>
         </is>
       </c>
       <c r="B329" s="5" t="n">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C329" s="6" t="n">
-        <v>0.0001187536990819573</v>
+        <v>0.0001182748535211429</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDU07CUX01  Apertura </t>
+          <t>SUA01CUX17 Apertura</t>
         </is>
       </c>
       <c r="B330" s="5" t="n">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C330" s="6" t="n">
-        <v>0.0001187536990819573</v>
+        <v>0.0001177960079603286</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>CU11CUX02 Apertura</t>
+          <t>CU02CUX01 Complejo Teatral</t>
         </is>
       </c>
       <c r="B331" s="5" t="n">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C331" s="6" t="n">
-        <v>0.0001182748535211429</v>
+        <v>0.0001168383168386999</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>SUA01CUX17 Apertura</t>
+          <t>SE02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B332" s="5" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C332" s="6" t="n">
-        <v>0.0001177960079603286</v>
+        <v>0.0001168383168386999</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>DH01CUX04 Pregunta 1</t>
+          <t>SA07CUX01 Anticonceptivos</t>
         </is>
       </c>
       <c r="B333" s="5" t="n">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C333" s="6" t="n">
-        <v>0.0001149229345954425</v>
+        <v>0.0001158806257170712</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>CU04CUX01 Apertura</t>
+          <t>DH01CUX04 Pregunta 1</t>
         </is>
       </c>
       <c r="B334" s="5" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C334" s="6" t="n">
-        <v>0.0001144440890346282</v>
+        <v>0.0001149229345954425</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>SA13CUX01 Apertura</t>
+          <t>CU04CUX01 Apertura</t>
         </is>
       </c>
       <c r="B335" s="5" t="n">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="C335" s="6" t="n">
-        <v>0.0001125287067913708</v>
+        <v>0.0001144440890346282</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>CO12CUX02 Temporal en BA</t>
+          <t>AGC01CUX00 Hacer una consulta</t>
         </is>
       </c>
       <c r="B336" s="5" t="n">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C336" s="6" t="n">
-        <v>0.0001125287067913708</v>
+        <v>0.0001134863979129995</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>DH08CUX02  Apertura estático principal</t>
+          <t>EDU04CUX24 Apertura</t>
         </is>
       </c>
       <c r="B337" s="5" t="n">
@@ -4838,7 +4838,7 @@
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>EDU04CUX24 Apertura</t>
+          <t>SA13CUX01 Apertura</t>
         </is>
       </c>
       <c r="B338" s="5" t="n">
@@ -4851,40 +4851,40 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>CU02CUX01 Complejo Teatral</t>
+          <t>DH08CUX02  Apertura estático principal</t>
         </is>
       </c>
       <c r="B339" s="5" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C339" s="6" t="n">
-        <v>0.0001120498612305565</v>
+        <v>0.0001125287067913708</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>CU01CUX01 Apertura</t>
+          <t>CO12CUX02 Temporal en BA</t>
         </is>
       </c>
       <c r="B340" s="5" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C340" s="6" t="n">
-        <v>0.0001110921701089278</v>
+        <v>0.0001120498612305565</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>MO05CUX13 Chequeo turno</t>
+          <t>CU01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B341" s="5" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C341" s="6" t="n">
-        <v>0.0001106133245481134</v>
+        <v>0.0001110921701089278</v>
       </c>
     </row>
     <row r="342">
@@ -4903,14 +4903,14 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>AGC01CUX00 Hacer una consulta</t>
+          <t>Registro de Establecimientos Gastronómicos</t>
         </is>
       </c>
       <c r="B343" s="5" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C343" s="6" t="n">
-        <v>0.0001082190967440417</v>
+        <v>0.0001077402511832274</v>
       </c>
     </row>
     <row r="344">
@@ -4920,29 +4920,29 @@
         </is>
       </c>
       <c r="B344" s="5" t="n">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C344" s="6" t="n">
-        <v>0.0001082190967440417</v>
+        <v>0.0001077402511832274</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Registro de Establecimientos Gastronómicos</t>
+          <t>TR03CUX30 Apertura</t>
         </is>
       </c>
       <c r="B345" s="5" t="n">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C345" s="6" t="n">
-        <v>0.0001077402511832274</v>
+        <v>0.000107261405622413</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>TR03CUX30 Apertura</t>
+          <t>TU03CUX11 Apertura</t>
         </is>
       </c>
       <c r="B346" s="5" t="n">
@@ -4955,170 +4955,170 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>TU03CUX11 Apertura</t>
+          <t>MO05CUX13 Chequeo turno</t>
         </is>
       </c>
       <c r="B347" s="5" t="n">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C347" s="6" t="n">
-        <v>0.000107261405622413</v>
+        <v>0.0001067825600615987</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>CIU05CUX12 Apertura de encuesta</t>
+          <t>CU01CUX02 Apertura</t>
         </is>
       </c>
       <c r="B348" s="5" t="n">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C348" s="6" t="n">
-        <v>0.00010582486893997</v>
+        <v>0.0001053460233791557</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>CU01CUX02 Apertura</t>
+          <t>TR03CUX16 Consorcios</t>
         </is>
       </c>
       <c r="B349" s="5" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C349" s="6" t="n">
-        <v>0.0001048671778183413</v>
+        <v>0.0001053460233791557</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>TR01CUX10 Apertura</t>
+          <t>CU08CUX06 Apertura</t>
         </is>
       </c>
       <c r="B350" s="5" t="n">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="C350" s="6" t="n">
-        <v>0.0001029517955750839</v>
+        <v>0.0001053460233791557</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>TU03CUX04 Apertura</t>
+          <t>TR01CUX10 Apertura</t>
         </is>
       </c>
       <c r="B351" s="5" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C351" s="6" t="n">
-        <v>0.0001024729500142696</v>
+        <v>0.0001029517955750839</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>VI01CUX06 Apertura</t>
+          <t>TU03CUX04 Apertura</t>
         </is>
       </c>
       <c r="B352" s="5" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C352" s="6" t="n">
-        <v>0.0001019941044534553</v>
+        <v>0.0001024729500142696</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>SE01CUX07 Apertura</t>
+          <t>VI01CUX06 Apertura</t>
         </is>
       </c>
       <c r="B353" s="5" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C353" s="6" t="n">
-        <v>0.0001015152588926409</v>
+        <v>0.0001019941044534553</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>TR03CUX16 Consorcios</t>
+          <t>SE01CUX07 Apertura</t>
         </is>
       </c>
       <c r="B354" s="5" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C354" s="6" t="n">
-        <v>0.0001010364133318266</v>
+        <v>0.0001015152588926409</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>DDHH03CUX06 Apertura</t>
+          <t>TR02CUX13 Cómo es el trámite</t>
         </is>
       </c>
       <c r="B355" s="5" t="n">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="C355" s="6" t="n">
-        <v>9.768449440612616e-05</v>
+        <v>9.864218552775484e-05</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t xml:space="preserve">DH11CUX06 Apertura </t>
+          <t>DDHH03CUX06 Apertura</t>
         </is>
       </c>
       <c r="B356" s="5" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C356" s="6" t="n">
-        <v>9.624795772368313e-05</v>
+        <v>9.768449440612616e-05</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>CU08CUX06 Apertura</t>
+          <t xml:space="preserve">DH11CUX06 Apertura </t>
         </is>
       </c>
       <c r="B357" s="5" t="n">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C357" s="6" t="n">
-        <v>9.529026660205444e-05</v>
+        <v>9.624795772368313e-05</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>MO10CUX03 Apertura</t>
+          <t>CIU05CUX12 Apertura de encuesta</t>
         </is>
       </c>
       <c r="B358" s="5" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C358" s="6" t="n">
-        <v>9.481142104124009e-05</v>
+        <v>9.529026660205444e-05</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>TR04CUX31 Qué necesito</t>
+          <t>MO10CUX03 Apertura</t>
         </is>
       </c>
       <c r="B359" s="5" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C359" s="6" t="n">
-        <v>9.145950211553969e-05</v>
+        <v>9.481142104124009e-05</v>
       </c>
     </row>
     <row r="360">
@@ -5150,14 +5150,14 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>ED03CUX05 Oferta académica</t>
+          <t>TR04CUX31 Qué necesito</t>
         </is>
       </c>
       <c r="B362" s="5" t="n">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C362" s="6" t="n">
-        <v>8.906527431146797e-05</v>
+        <v>8.858642875065363e-05</v>
       </c>
     </row>
     <row r="363">
@@ -5176,27 +5176,27 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>TR02CUX13 Cómo es el trámite</t>
+          <t>CO02CUX02 Apertura</t>
         </is>
       </c>
       <c r="B364" s="5" t="n">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C364" s="6" t="n">
-        <v>8.858642875065363e-05</v>
+        <v>8.810758318983928e-05</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>CO02CUX02 Apertura</t>
+          <t>ED03CUX05 Oferta académica</t>
         </is>
       </c>
       <c r="B365" s="5" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C365" s="6" t="n">
-        <v>8.810758318983928e-05</v>
+        <v>8.714989206821059e-05</v>
       </c>
     </row>
     <row r="366">
@@ -5215,33 +5215,33 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>TR01CUX08 Apertura</t>
+          <t>TR04CUX41 Mi argentina</t>
         </is>
       </c>
       <c r="B367" s="5" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C367" s="6" t="n">
-        <v>8.523450982495321e-05</v>
+        <v>8.571335538576756e-05</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>SE02CUX03 Apertura</t>
+          <t>TR01CUX08 Apertura</t>
         </is>
       </c>
       <c r="B368" s="5" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C368" s="6" t="n">
-        <v>8.427681870332453e-05</v>
+        <v>8.475566426413888e-05</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>CU10CUX01 Apertura</t>
+          <t>SE02CUX03 Apertura</t>
         </is>
       </c>
       <c r="B369" s="5" t="n">
@@ -5254,14 +5254,14 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>EDU03CUX08 Necesito ayuda</t>
+          <t>CU10CUX01 Apertura</t>
         </is>
       </c>
       <c r="B370" s="5" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C370" s="6" t="n">
-        <v>8.379797314251019e-05</v>
+        <v>8.427681870332453e-05</v>
       </c>
     </row>
     <row r="371">
@@ -5271,23 +5271,23 @@
         </is>
       </c>
       <c r="B371" s="5" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C371" s="6" t="n">
-        <v>8.236143646006715e-05</v>
+        <v>8.427681870332453e-05</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>CU01CUX14 Apertura Estático</t>
+          <t>EDU03CUX08 Necesito ayuda</t>
         </is>
       </c>
       <c r="B372" s="5" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C372" s="6" t="n">
-        <v>8.236143646006715e-05</v>
+        <v>8.379797314251019e-05</v>
       </c>
     </row>
     <row r="373">
@@ -5306,7 +5306,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Mensaje Otra Dirección | Permitido Estacionar</t>
+          <t>AM04CUX02 Apertura</t>
         </is>
       </c>
       <c r="B374" s="5" t="n">
@@ -5319,14 +5319,14 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>EDU04CUX23 Apertura</t>
+          <t>Mensaje Otra Dirección | Permitido Estacionar</t>
         </is>
       </c>
       <c r="B375" s="5" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C375" s="6" t="n">
-        <v>8.092489977762413e-05</v>
+        <v>8.140374533843846e-05</v>
       </c>
     </row>
     <row r="376">
@@ -5345,7 +5345,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>AM04CUX02 Apertura</t>
+          <t>EDU04CUX23 Apertura</t>
         </is>
       </c>
       <c r="B377" s="5" t="n">
@@ -5358,111 +5358,111 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>DH06CUX01 Apertura</t>
+          <t>Permiso de espectáculos musicales en vivo</t>
         </is>
       </c>
       <c r="B378" s="5" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C378" s="6" t="n">
-        <v>8.092489977762413e-05</v>
+        <v>8.044605421680977e-05</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>SUA01CUX Descripción opcional</t>
+          <t>Cariño</t>
         </is>
       </c>
       <c r="B379" s="5" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C379" s="6" t="n">
-        <v>8.092489977762413e-05</v>
+        <v>7.996720865599544e-05</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>TR04CUX41 Mi argentina</t>
+          <t>VI01CUX02 Apertura</t>
         </is>
       </c>
       <c r="B380" s="5" t="n">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C380" s="6" t="n">
-        <v>8.044605421680977e-05</v>
+        <v>7.996720865599544e-05</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Permiso de espectáculos musicales en vivo</t>
+          <t>DH06CUX01 Apertura</t>
         </is>
       </c>
       <c r="B381" s="5" t="n">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C381" s="6" t="n">
-        <v>8.044605421680977e-05</v>
+        <v>7.948836309518109e-05</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>VI01CUX02 Apertura</t>
+          <t>AC02CUX02 Apertura</t>
         </is>
       </c>
       <c r="B382" s="5" t="n">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C382" s="6" t="n">
-        <v>7.996720865599544e-05</v>
+        <v>7.948836309518109e-05</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Cariño</t>
+          <t>Suaci - Error de foto opcional</t>
         </is>
       </c>
       <c r="B383" s="5" t="n">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C383" s="6" t="n">
-        <v>7.996720865599544e-05</v>
+        <v>7.900951753436675e-05</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>AC02CUX02 Apertura</t>
+          <t>INN09CUX01 Apertura</t>
         </is>
       </c>
       <c r="B384" s="5" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C384" s="6" t="n">
-        <v>7.948836309518109e-05</v>
+        <v>7.85306719735524e-05</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>INN09CUX01 Apertura</t>
+          <t>MO10CUX02 Apertura</t>
         </is>
       </c>
       <c r="B385" s="5" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C385" s="6" t="n">
-        <v>7.900951753436675e-05</v>
+        <v>7.805182641273806e-05</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Suaci - Error de foto opcional</t>
+          <t>MO05CUX10 Apertura</t>
         </is>
       </c>
       <c r="B386" s="5" t="n">
@@ -5475,150 +5475,150 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>MO05CUX10 Apertura</t>
+          <t>NI01CUX12 Botimisterios</t>
         </is>
       </c>
       <c r="B387" s="5" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C387" s="6" t="n">
-        <v>7.805182641273806e-05</v>
+        <v>7.709413529110937e-05</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>MO10CUX02 Apertura</t>
+          <t>DDHH02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B388" s="5" t="n">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C388" s="6" t="n">
-        <v>7.805182641273806e-05</v>
+        <v>7.661528973029502e-05</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>NI01CUX12 Botimisterios</t>
+          <t>CU04CUX32 Apertura post evento</t>
         </is>
       </c>
       <c r="B389" s="5" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C389" s="6" t="n">
-        <v>7.709413529110937e-05</v>
+        <v>7.661528973029502e-05</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>TUR01CUX12 Pedir tipo de documento</t>
+          <t>EDU03CUX06 Apertura</t>
         </is>
       </c>
       <c r="B390" s="5" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C390" s="6" t="n">
-        <v>7.709413529110937e-05</v>
+        <v>7.661528973029502e-05</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>DDHH02CUX01 Apertura</t>
+          <t>MO06CUX03 Apertura</t>
         </is>
       </c>
       <c r="B391" s="5" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C391" s="6" t="n">
-        <v>7.661528973029502e-05</v>
+        <v>7.613644416948069e-05</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>EDU03CUX06 Apertura</t>
+          <t>AG01CUX01 Inmobiliario/ABL</t>
         </is>
       </c>
       <c r="B392" s="5" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C392" s="6" t="n">
-        <v>7.661528973029502e-05</v>
+        <v>7.565759860866634e-05</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>CU04CUX32 Apertura post evento</t>
+          <t>TR03CUX09 Ruidos molestos provenientes de actividades comerciales e industriales</t>
         </is>
       </c>
       <c r="B393" s="5" t="n">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C393" s="6" t="n">
-        <v>7.661528973029502e-05</v>
+        <v>7.565759860866634e-05</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>MO06CUX03 Apertura</t>
+          <t>MO05CUX11 Pregunta enfermedad neurológica</t>
         </is>
       </c>
       <c r="B394" s="5" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C394" s="6" t="n">
-        <v>7.613644416948069e-05</v>
+        <v>7.565759860866634e-05</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>TR03CUX09 Ruidos molestos provenientes de actividades comerciales e industriales</t>
+          <t>EDU04CUX29 Apertura</t>
         </is>
       </c>
       <c r="B395" s="5" t="n">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C395" s="6" t="n">
-        <v>7.565759860866634e-05</v>
+        <v>7.5178753047852e-05</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>AG01CUX01 Inmobiliario/ABL</t>
+          <t>GE01CUX03 Apertura</t>
         </is>
       </c>
       <c r="B396" s="5" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C396" s="6" t="n">
-        <v>7.565759860866634e-05</v>
+        <v>7.469990748703765e-05</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>MO05CUX11 Pregunta enfermedad cardíaca</t>
+          <t>SE02CUX02 Apertura</t>
         </is>
       </c>
       <c r="B397" s="5" t="n">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C397" s="6" t="n">
-        <v>7.565759860866634e-05</v>
+        <v>7.469990748703765e-05</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>TU01CUX05 Apertura</t>
+          <t>MO10CUX08 Apertura</t>
         </is>
       </c>
       <c r="B398" s="5" t="n">
@@ -5631,92 +5631,92 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>GE01CUX03 Apertura</t>
+          <t>CU01CUX14 Apertura Estático</t>
         </is>
       </c>
       <c r="B399" s="5" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C399" s="6" t="n">
-        <v>7.469990748703765e-05</v>
+        <v>7.422106192622331e-05</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>EDU04CUX29 Apertura</t>
+          <t>PC03CUX01 Apertura</t>
         </is>
       </c>
       <c r="B400" s="5" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C400" s="6" t="n">
-        <v>7.469990748703765e-05</v>
+        <v>7.422106192622331e-05</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>SE02CUX02 Apertura</t>
+          <t>TU01CUX05 Apertura</t>
         </is>
       </c>
       <c r="B401" s="5" t="n">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C401" s="6" t="n">
-        <v>7.469990748703765e-05</v>
+        <v>7.374221636540896e-05</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>MO10CUX08 Apertura</t>
+          <t>DE01CUX02 Apertura post-evento</t>
         </is>
       </c>
       <c r="B402" s="5" t="n">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C402" s="6" t="n">
-        <v>7.469990748703765e-05</v>
+        <v>7.278452524378027e-05</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>DE01CUX02 Apertura post-evento</t>
+          <t>DE05CUX02 Qué actividades hay</t>
         </is>
       </c>
       <c r="B403" s="5" t="n">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C403" s="6" t="n">
-        <v>7.278452524378027e-05</v>
+        <v>7.134798856133725e-05</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>TR03CUX08 Apertura</t>
+          <t>EDU05CUX05 Apertura</t>
         </is>
       </c>
       <c r="B404" s="5" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C404" s="6" t="n">
-        <v>7.230567968296594e-05</v>
+        <v>7.08691430005229e-05</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>PC03CUX01 Apertura</t>
+          <t>AGC01CUX00  Apertura</t>
         </is>
       </c>
       <c r="B405" s="5" t="n">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C405" s="6" t="n">
-        <v>7.230567968296594e-05</v>
+        <v>7.08691430005229e-05</v>
       </c>
     </row>
     <row r="406">
@@ -5735,7 +5735,7 @@
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>TR02CUX13 Qué necesito</t>
+          <t>TR03CUX08 Apertura</t>
         </is>
       </c>
       <c r="B407" s="5" t="n">
@@ -5748,7 +5748,7 @@
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>EDU05CUX05 Apertura</t>
+          <t>TR04CUX08 Asiento de la defunción en la libreta de matrimonio</t>
         </is>
       </c>
       <c r="B408" s="5" t="n">
@@ -5761,521 +5761,521 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>TR04CUX08 Asiento de la defunción en la libreta de matrimonio</t>
+          <t>DEC01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B409" s="5" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C409" s="6" t="n">
-        <v>6.943260631807987e-05</v>
+        <v>6.847491519645118e-05</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>AGC01CUX00  Apertura</t>
+          <t>GA03CUX10 Apertura</t>
         </is>
       </c>
       <c r="B410" s="5" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C410" s="6" t="n">
-        <v>6.943260631807987e-05</v>
+        <v>6.799606963563683e-05</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>DEC01CUX01 Apertura</t>
+          <t>EDU04CUX19 Tengo una consulta</t>
         </is>
       </c>
       <c r="B411" s="5" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="C411" s="6" t="n">
-        <v>6.895376075726552e-05</v>
+        <v>6.75172240748225e-05</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>GA03CUX10 Apertura</t>
+          <t>CIU02CUX01 Sedes comunales</t>
         </is>
       </c>
       <c r="B412" s="5" t="n">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C412" s="6" t="n">
-        <v>6.799606963563683e-05</v>
+        <v>6.416530514912208e-05</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>EDU04CUX19 Tengo una consulta</t>
+          <t>MO04CUX10 Apertura</t>
         </is>
       </c>
       <c r="B413" s="5" t="n">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="C413" s="6" t="n">
-        <v>6.75172240748225e-05</v>
+        <v>6.416530514912208e-05</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>TR02CUX14 Nacimiento</t>
+          <t>CU01CUX05 Apertura</t>
         </is>
       </c>
       <c r="B414" s="5" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="C414" s="6" t="n">
-        <v>6.703837851400815e-05</v>
+        <v>6.416530514912208e-05</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>DE05CUX02 Qué actividades hay</t>
+          <t>INN10CUX01 Apertura</t>
         </is>
       </c>
       <c r="B415" s="5" t="n">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="C415" s="6" t="n">
-        <v>6.655953295319381e-05</v>
+        <v>6.320761402749339e-05</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>MO02CUX01 Apertura</t>
+          <t>TR02CUX13 Qué necesito</t>
         </is>
       </c>
       <c r="B416" s="5" t="n">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C416" s="6" t="n">
-        <v>6.512299627075077e-05</v>
+        <v>6.272876846667906e-05</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>CU01CUX05 Apertura</t>
+          <t>MO02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B417" s="5" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="C417" s="6" t="n">
-        <v>6.416530514912208e-05</v>
+        <v>6.081338622342168e-05</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>MO04CUX10 Apertura</t>
+          <t>Viaductos</t>
         </is>
       </c>
       <c r="B418" s="5" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C418" s="6" t="n">
-        <v>6.416530514912208e-05</v>
+        <v>6.033454066260733e-05</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CIU02CUX01 Sedes comunales</t>
+          <t>GE03CUX02 Busco trabajo</t>
         </is>
       </c>
       <c r="B419" s="5" t="n">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="C419" s="6" t="n">
-        <v>6.416530514912208e-05</v>
+        <v>6.033454066260733e-05</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>TU03CUX09 Apertura</t>
+          <t>AM04CUX04 Apertura</t>
         </is>
       </c>
       <c r="B420" s="5" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="C420" s="6" t="n">
-        <v>6.320761402749339e-05</v>
+        <v>5.985569510179299e-05</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>INN10CUX01 Apertura</t>
+          <t>TU03CUX09 Apertura</t>
         </is>
       </c>
       <c r="B421" s="5" t="n">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="C421" s="6" t="n">
-        <v>6.272876846667906e-05</v>
+        <v>5.985569510179299e-05</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>AM04CUX04 Apertura</t>
+          <t>DE00CUX03 Apertura</t>
         </is>
       </c>
       <c r="B422" s="5" t="n">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="C422" s="6" t="n">
-        <v>6.129223178423602e-05</v>
+        <v>5.937684954097864e-05</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Viaductos</t>
+          <t>MO05CUX13 Apertura</t>
         </is>
       </c>
       <c r="B423" s="5" t="n">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="C423" s="6" t="n">
-        <v>6.033454066260733e-05</v>
+        <v>5.88980039801643e-05</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>GE03CUX02 Busco trabajo</t>
+          <t>AC01CUX02 Gobierno Nacional</t>
         </is>
       </c>
       <c r="B424" s="5" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C424" s="6" t="n">
-        <v>5.937684954097864e-05</v>
+        <v>5.841915841934996e-05</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>DE00CUX03 Apertura</t>
+          <t>TR03CUX26 Apertura</t>
         </is>
       </c>
       <c r="B425" s="5" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C425" s="6" t="n">
-        <v>5.937684954097864e-05</v>
+        <v>5.841915841934996e-05</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>MO05CUX13 Apertura</t>
+          <t>CU08CUX02 Apertura de contingencia</t>
         </is>
       </c>
       <c r="B426" s="5" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C426" s="6" t="n">
-        <v>5.88980039801643e-05</v>
+        <v>5.794031285853561e-05</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>AC01CUX02 Gobierno Nacional</t>
+          <t>SA16CUX01 Monóxido de carbono</t>
         </is>
       </c>
       <c r="B427" s="5" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C427" s="6" t="n">
-        <v>5.841915841934996e-05</v>
+        <v>5.746146729772127e-05</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>TR03CUX26 Apertura</t>
+          <t>MO04CUX08 Mapa Interactivo</t>
         </is>
       </c>
       <c r="B428" s="5" t="n">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C428" s="6" t="n">
-        <v>5.841915841934996e-05</v>
+        <v>5.698262173690692e-05</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>CU08CUX02 Apertura de contingencia</t>
+          <t>CU11CUX03 Apertura</t>
         </is>
       </c>
       <c r="B429" s="5" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C429" s="6" t="n">
-        <v>5.794031285853561e-05</v>
+        <v>5.698262173690692e-05</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>SA16CUX01 Monóxido de carbono</t>
+          <t>Licencias Boti</t>
         </is>
       </c>
       <c r="B430" s="5" t="n">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C430" s="6" t="n">
-        <v>5.746146729772127e-05</v>
+        <v>5.602493061527824e-05</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>CU11CUX03 Apertura</t>
+          <t>CIU05CUX07 Apertura</t>
         </is>
       </c>
       <c r="B431" s="5" t="n">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C431" s="6" t="n">
-        <v>5.698262173690692e-05</v>
+        <v>5.554608505446389e-05</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>MO04CUX08 Mapa Interactivo</t>
+          <t>ED04CUX18 Apertura</t>
         </is>
       </c>
       <c r="B432" s="5" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C432" s="6" t="n">
-        <v>5.698262173690692e-05</v>
+        <v>5.506723949364955e-05</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>Licencias Boti</t>
+          <t>TR02CUX10 Confirmar trámite</t>
         </is>
       </c>
       <c r="B433" s="5" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C433" s="6" t="n">
-        <v>5.602493061527824e-05</v>
+        <v>5.45883939328352e-05</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>CIU05CUX07 Apertura</t>
+          <t>AM02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B434" s="5" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C434" s="6" t="n">
-        <v>5.554608505446389e-05</v>
+        <v>5.45883939328352e-05</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>ED04CUX18 Apertura</t>
+          <t>DDHH03CUX04 Apertura</t>
         </is>
       </c>
       <c r="B435" s="5" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C435" s="6" t="n">
-        <v>5.506723949364955e-05</v>
+        <v>5.410954837202086e-05</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>TR02CUX13 Partida de defunción SD</t>
+          <t>Certificación de datos</t>
         </is>
       </c>
       <c r="B436" s="5" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C436" s="6" t="n">
-        <v>5.45883939328352e-05</v>
+        <v>5.410954837202086e-05</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>TR02CUX10 Confirmar trámite</t>
+          <t>TR05CUX04 Apertura</t>
         </is>
       </c>
       <c r="B437" s="5" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C437" s="6" t="n">
-        <v>5.45883939328352e-05</v>
+        <v>5.363070281120652e-05</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>AM02CUX01 Apertura</t>
+          <t>TR03CUX05 Apertura</t>
         </is>
       </c>
       <c r="B438" s="5" t="n">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C438" s="6" t="n">
-        <v>5.45883939328352e-05</v>
+        <v>5.315185725039217e-05</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>TR03CUX05 Apertura</t>
+          <t>Boletín Oficial</t>
         </is>
       </c>
       <c r="B439" s="5" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C439" s="6" t="n">
-        <v>5.410954837202086e-05</v>
+        <v>5.267301168957783e-05</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Certificación de datos</t>
+          <t>Bicicletas (Apertura) &gt; Qué ciclovías hay * Response</t>
         </is>
       </c>
       <c r="B440" s="5" t="n">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C440" s="6" t="n">
-        <v>5.410954837202086e-05</v>
+        <v>5.219416612876348e-05</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>DDHH03CUX04 Apertura</t>
+          <t>MO06CUX01 Apertura</t>
         </is>
       </c>
       <c r="B441" s="5" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C441" s="6" t="n">
-        <v>5.363070281120652e-05</v>
+        <v>5.171532056794914e-05</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>DE03CUX02 Apertura</t>
+          <t xml:space="preserve">DH05CUX01 Apertura </t>
         </is>
       </c>
       <c r="B442" s="5" t="n">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C442" s="6" t="n">
-        <v>5.363070281120652e-05</v>
+        <v>5.12364750071348e-05</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>TUR01CUX12 Preguntar género</t>
+          <t>TR02CUX13 Partida de defunción SD</t>
         </is>
       </c>
       <c r="B443" s="5" t="n">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C443" s="6" t="n">
-        <v>5.315185725039217e-05</v>
+        <v>5.12364750071348e-05</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Boletín Oficial</t>
+          <t>CIU05CUX01 Autonomía</t>
         </is>
       </c>
       <c r="B444" s="5" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C444" s="6" t="n">
-        <v>5.267301168957783e-05</v>
+        <v>5.075762944632045e-05</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Bicicletas (Apertura) &gt; Qué ciclovías hay * Response</t>
+          <t>AM03CUX05 Superapertura</t>
         </is>
       </c>
       <c r="B445" s="5" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C445" s="6" t="n">
-        <v>5.219416612876348e-05</v>
+        <v>5.075762944632045e-05</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>CIU05CUX09 Parque Rivadavia</t>
+          <t>INN01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B446" s="5" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C446" s="6" t="n">
-        <v>5.171532056794914e-05</v>
+        <v>5.075762944632045e-05</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>MO06CUX01 Apertura</t>
+          <t>DE03CUX02 Apertura</t>
         </is>
       </c>
       <c r="B447" s="5" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C447" s="6" t="n">
-        <v>5.171532056794914e-05</v>
+        <v>5.075762944632045e-05</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>TR05CUX04 Apertura</t>
+          <t>EM04CUX02 Mujer Emprendedora</t>
         </is>
       </c>
       <c r="B448" s="5" t="n">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C448" s="6" t="n">
-        <v>5.12364750071348e-05</v>
+        <v>5.027878388550611e-05</v>
       </c>
     </row>
     <row r="449">
@@ -6285,36 +6285,36 @@
         </is>
       </c>
       <c r="B449" s="5" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C449" s="6" t="n">
-        <v>5.075762944632045e-05</v>
+        <v>5.027878388550611e-05</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>INN01CUX01 Apertura</t>
+          <t>TR02CUX05 - Apertura</t>
         </is>
       </c>
       <c r="B450" s="5" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C450" s="6" t="n">
-        <v>5.075762944632045e-05</v>
+        <v>4.932109276387742e-05</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>AM03CUX05 Superapertura</t>
+          <t>Webchat Identificar Customer</t>
         </is>
       </c>
       <c r="B451" s="5" t="n">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C451" s="6" t="n">
-        <v>5.075762944632045e-05</v>
+        <v>4.884224720306308e-05</v>
       </c>
     </row>
     <row r="452">
@@ -6324,536 +6324,536 @@
         </is>
       </c>
       <c r="B452" s="5" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C452" s="6" t="n">
-        <v>5.027878388550611e-05</v>
+        <v>4.884224720306308e-05</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>CIU05CUX01 Autonomía</t>
+          <t>CU04CUX41 Apertura</t>
         </is>
       </c>
       <c r="B453" s="5" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C453" s="6" t="n">
-        <v>5.027878388550611e-05</v>
+        <v>4.836340164224873e-05</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>EM04CUX02 Mujer Emprendedora</t>
+          <t>TUR01CUX06 Turnos disponibles en esa franja horaria</t>
         </is>
       </c>
       <c r="B454" s="5" t="n">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="C454" s="6" t="n">
-        <v>4.979993832469177e-05</v>
+        <v>4.644801939899136e-05</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>TR02CUX05 - Apertura</t>
+          <t>¿Algo más? |  Buscar comunas</t>
         </is>
       </c>
       <c r="B455" s="5" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C455" s="6" t="n">
-        <v>4.932109276387742e-05</v>
+        <v>4.596917383817701e-05</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>Webchat Identificar Customer</t>
+          <t>Comuna Encontrada | Buscar comunas</t>
         </is>
       </c>
       <c r="B456" s="5" t="n">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C456" s="6" t="n">
-        <v>4.884224720306308e-05</v>
+        <v>4.596917383817701e-05</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>CU04CUX41 Apertura</t>
+          <t>INN10CUX06 Validación audios largos</t>
         </is>
       </c>
       <c r="B457" s="5" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C457" s="6" t="n">
-        <v>4.836340164224873e-05</v>
+        <v>4.501148271654833e-05</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t xml:space="preserve">DH05CUX01 Apertura </t>
+          <t>SE01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B458" s="5" t="n">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="C458" s="6" t="n">
-        <v>4.740571052062005e-05</v>
+        <v>4.453263715573398e-05</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>TUR01CUX06 Turnos disponibles en esa franja horaria</t>
+          <t>MO05CUX03 Apertura</t>
         </is>
       </c>
       <c r="B459" s="5" t="n">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C459" s="6" t="n">
-        <v>4.644801939899136e-05</v>
+        <v>4.453263715573398e-05</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>¿Algo más? |  Buscar comunas</t>
+          <t>El usuario ha enviado una ubicación</t>
         </is>
       </c>
       <c r="B460" s="5" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C460" s="6" t="n">
-        <v>4.596917383817701e-05</v>
+        <v>4.453263715573398e-05</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>Comuna Encontrada | Buscar comunas</t>
+          <t>DEC03CUX01 Apertura</t>
         </is>
       </c>
       <c r="B461" s="5" t="n">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C461" s="6" t="n">
-        <v>4.596917383817701e-05</v>
+        <v>4.453263715573398e-05</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>INN10CUX06 Validación audios largos</t>
+          <t>TR01CUX18  Apertura</t>
         </is>
       </c>
       <c r="B462" s="5" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C462" s="6" t="n">
-        <v>4.501148271654833e-05</v>
+        <v>4.405379159491964e-05</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>El usuario ha enviado una ubicación</t>
+          <t>SUA01CUX27 Pedido de dirección</t>
         </is>
       </c>
       <c r="B463" s="5" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C463" s="6" t="n">
-        <v>4.453263715573398e-05</v>
+        <v>4.357494603410529e-05</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>DEC03CUX01 Apertura</t>
+          <t>DDHH03CUX09 Apertura</t>
         </is>
       </c>
       <c r="B464" s="5" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C464" s="6" t="n">
-        <v>4.453263715573398e-05</v>
+        <v>4.261725491247661e-05</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>MO05CUX03 Apertura</t>
+          <t>TR03CUX06 Apertura</t>
         </is>
       </c>
       <c r="B465" s="5" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C465" s="6" t="n">
-        <v>4.453263715573398e-05</v>
+        <v>4.261725491247661e-05</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>TR03CUX06 Apertura</t>
+          <t>EDU02CUX09 Apertura</t>
         </is>
       </c>
       <c r="B466" s="5" t="n">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C466" s="6" t="n">
-        <v>4.453263715573398e-05</v>
+        <v>4.261725491247661e-05</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>TR01CUX18  Apertura</t>
+          <t>TU03CUX01 Apertura fútbol</t>
         </is>
       </c>
       <c r="B467" s="5" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C467" s="6" t="n">
-        <v>4.405379159491964e-05</v>
+        <v>4.261725491247661e-05</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>TU03CUX01 Apertura fútbol</t>
+          <t>MO10CUX01 Apertura</t>
         </is>
       </c>
       <c r="B468" s="5" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C468" s="6" t="n">
-        <v>4.357494603410529e-05</v>
+        <v>4.213840935166226e-05</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>SE01CUX01 Apertura</t>
+          <t>AUSA (Apertura) &gt; Ver estado de cuenta (Apertura) &gt; Si no tiene saldos a pagar * Response</t>
         </is>
       </c>
       <c r="B469" s="5" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C469" s="6" t="n">
-        <v>4.357494603410529e-05</v>
+        <v>4.213840935166226e-05</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>DDHH03CUX09 Apertura</t>
+          <t>Final | Búsqueda de Farmacias</t>
         </is>
       </c>
       <c r="B470" s="5" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C470" s="6" t="n">
-        <v>4.357494603410529e-05</v>
+        <v>4.165956379084792e-05</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>EDU02CUX09 Apertura</t>
+          <t>DDHH01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B471" s="5" t="n">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C471" s="6" t="n">
-        <v>4.261725491247661e-05</v>
+        <v>4.118071823003358e-05</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>AUSA (Apertura) &gt; Ver estado de cuenta (Apertura) &gt; Si no tiene saldos a pagar * Response</t>
+          <t>SUA01CUX15 Dirección</t>
         </is>
       </c>
       <c r="B472" s="5" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C472" s="6" t="n">
-        <v>4.213840935166226e-05</v>
+        <v>4.070187266921923e-05</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>MO10CUX01 Apertura</t>
+          <t>EM03CUX02 Apertura</t>
         </is>
       </c>
       <c r="B473" s="5" t="n">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C473" s="6" t="n">
-        <v>4.165956379084792e-05</v>
+        <v>4.022302710840489e-05</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Final | Búsqueda de Farmacias</t>
+          <t>¿Quien sos?</t>
         </is>
       </c>
       <c r="B474" s="5" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C474" s="6" t="n">
-        <v>4.165956379084792e-05</v>
+        <v>3.974418154759054e-05</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>SUA01CUX15 Dirección</t>
+          <t>Certificado de matrícula</t>
         </is>
       </c>
       <c r="B475" s="5" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C475" s="6" t="n">
-        <v>4.118071823003358e-05</v>
+        <v>3.974418154759054e-05</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>DDHH01CUX01 Apertura</t>
+          <t>MO10CUX06 Apertura</t>
         </is>
       </c>
       <c r="B476" s="5" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C476" s="6" t="n">
-        <v>4.070187266921923e-05</v>
+        <v>3.974418154759054e-05</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>SUA01CUX27 Pedido de dirección</t>
+          <t>TU03CUX10 Apertura</t>
         </is>
       </c>
       <c r="B477" s="5" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C477" s="6" t="n">
-        <v>3.974418154759054e-05</v>
+        <v>3.878649042596186e-05</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>¿Quien sos?</t>
+          <t>TR01CUX15 Apertura</t>
         </is>
       </c>
       <c r="B478" s="5" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C478" s="6" t="n">
-        <v>3.974418154759054e-05</v>
+        <v>3.878649042596186e-05</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>Certificado de matrícula</t>
+          <t>TUR01CUX12 Pedir tipo de documento</t>
         </is>
       </c>
       <c r="B479" s="5" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C479" s="6" t="n">
-        <v>3.974418154759054e-05</v>
+        <v>3.878649042596186e-05</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>SE01CUX04 Apertura</t>
+          <t>SE06CUX01 Apertura</t>
         </is>
       </c>
       <c r="B480" s="5" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C480" s="6" t="n">
-        <v>3.878649042596186e-05</v>
+        <v>3.830764486514751e-05</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>TU03CUX10 Apertura</t>
+          <t>SE01CUX04 Apertura</t>
         </is>
       </c>
       <c r="B481" s="5" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C481" s="6" t="n">
-        <v>3.878649042596186e-05</v>
+        <v>3.830764486514751e-05</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>MO10CUX06 Apertura</t>
+          <t>DH11CUX02 Chat por whatsapp</t>
         </is>
       </c>
       <c r="B482" s="5" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C482" s="6" t="n">
-        <v>3.878649042596186e-05</v>
+        <v>3.734995374351882e-05</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>EM03CUX02 Apertura</t>
+          <t>TR03CUX07 Apertura Inscripción en el Registro Único de Instituciones Deportivas (RUID)</t>
         </is>
       </c>
       <c r="B483" s="5" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C483" s="6" t="n">
-        <v>3.782879930433317e-05</v>
+        <v>3.639226262189014e-05</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>TR01CUX15 Apertura</t>
+          <t>AM03CUX04 Apertura Ambiente</t>
         </is>
       </c>
       <c r="B484" s="5" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C484" s="6" t="n">
-        <v>3.687110818270448e-05</v>
+        <v>3.543457150026145e-05</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>SE06CUX01 Apertura</t>
+          <t>CIU05CUX09 Parque Rivadavia</t>
         </is>
       </c>
       <c r="B485" s="5" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C485" s="6" t="n">
-        <v>3.687110818270448e-05</v>
+        <v>3.543457150026145e-05</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>DH11CUX02 Chat por whatsapp</t>
+          <t xml:space="preserve">Cómo lo renuevo | Certificado de residencia precaria </t>
         </is>
       </c>
       <c r="B486" s="5" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C486" s="6" t="n">
-        <v>3.687110818270448e-05</v>
+        <v>3.447688037863276e-05</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>TR03CUX07 Apertura Inscripción en el Registro Único de Instituciones Deportivas (RUID)</t>
+          <t>Deficiencias en la gestión</t>
         </is>
       </c>
       <c r="B487" s="5" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C487" s="6" t="n">
-        <v>3.639226262189014e-05</v>
+        <v>3.399803481781842e-05</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>AM03CUX04 Apertura Ambiente</t>
+          <t>TR01CUX09 Apertura</t>
         </is>
       </c>
       <c r="B488" s="5" t="n">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C488" s="6" t="n">
-        <v>3.543457150026145e-05</v>
+        <v>3.351918925700407e-05</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>DH11CUX03 Silencio user</t>
+          <t xml:space="preserve">Qué necesito | Certificado de residencia precaria </t>
         </is>
       </c>
       <c r="B489" s="5" t="n">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C489" s="6" t="n">
-        <v>3.49557259394471e-05</v>
+        <v>3.304034369618973e-05</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>DH07CUX01 Apertura</t>
+          <t>AM04CUX01 Qué hay para hacer</t>
         </is>
       </c>
       <c r="B490" s="5" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C490" s="6" t="n">
-        <v>3.399803481781842e-05</v>
+        <v>3.256149813537539e-05</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>Deficiencias en la gestión</t>
+          <t>DH07CUX01 Apertura</t>
         </is>
       </c>
       <c r="B491" s="5" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C491" s="6" t="n">
-        <v>3.399803481781842e-05</v>
+        <v>3.256149813537539e-05</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cómo lo tramito | Certificado de residencia precaria </t>
+          <t xml:space="preserve">NI01CUX05 Boticuentos </t>
         </is>
       </c>
       <c r="B492" s="5" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C492" s="6" t="n">
-        <v>3.351918925700407e-05</v>
+        <v>3.256149813537539e-05</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>AM04CUX01 Qué hay para hacer</t>
+          <t>DH11CUX03 Silencio user</t>
         </is>
       </c>
       <c r="B493" s="5" t="n">
@@ -6866,137 +6866,137 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qué necesito | Certificado de residencia precaria </t>
+          <t>Derivación a Boti</t>
         </is>
       </c>
       <c r="B494" s="5" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C494" s="6" t="n">
-        <v>3.256149813537539e-05</v>
+        <v>3.208265257456104e-05</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t xml:space="preserve">NI01CUX05 Boticuentos </t>
+          <t>TR04CUX31 Cómo lo hago</t>
         </is>
       </c>
       <c r="B495" s="5" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C495" s="6" t="n">
-        <v>3.256149813537539e-05</v>
+        <v>3.16038070137467e-05</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>Derivación a Boti</t>
+          <t>DH11CUX02 Apertura</t>
         </is>
       </c>
       <c r="B496" s="5" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C496" s="6" t="n">
-        <v>3.16038070137467e-05</v>
+        <v>3.064611589211801e-05</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>DDHH03CUX02 Apertura</t>
+          <t>Feedback a humano - Unificado</t>
         </is>
       </c>
       <c r="B497" s="5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C497" s="6" t="n">
-        <v>3.112496145293235e-05</v>
+        <v>3.016727033130367e-05</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>DH11CUX02 Apertura</t>
+          <t xml:space="preserve">Cómo lo tramito | Certificado de residencia precaria </t>
         </is>
       </c>
       <c r="B498" s="5" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C498" s="6" t="n">
-        <v>3.112496145293235e-05</v>
+        <v>3.016727033130367e-05</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>TR01CUX09 Apertura</t>
+          <t>AM02CUX02 Consejos</t>
         </is>
       </c>
       <c r="B499" s="5" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C499" s="6" t="n">
-        <v>3.112496145293235e-05</v>
+        <v>2.968842477048932e-05</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>CU09CUX03 Apertura</t>
+          <t>DDHH03CUX02 Apertura</t>
         </is>
       </c>
       <c r="B500" s="5" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C500" s="6" t="n">
-        <v>3.016727033130367e-05</v>
+        <v>2.968842477048932e-05</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>Feedback a humano - Unificado</t>
+          <t>CU09CUX03 Apertura</t>
         </is>
       </c>
       <c r="B501" s="5" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C501" s="6" t="n">
-        <v>3.016727033130367e-05</v>
+        <v>2.920957920967498e-05</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>AM02CUX02 Consejos</t>
+          <t>CU04CUX42 Apertura</t>
         </is>
       </c>
       <c r="B502" s="5" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C502" s="6" t="n">
-        <v>2.968842477048932e-05</v>
+        <v>2.873073364886063e-05</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cómo lo renuevo | Certificado de residencia precaria </t>
+          <t>TU03CUX03 Apertura</t>
         </is>
       </c>
       <c r="B503" s="5" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C503" s="6" t="n">
-        <v>2.920957920967498e-05</v>
+        <v>2.873073364886063e-05</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>TR04CUX31 Cómo lo hago</t>
+          <t xml:space="preserve">TR04CUX32  Errores en pasaporte </t>
         </is>
       </c>
       <c r="B504" s="5" t="n">
@@ -7009,475 +7009,475 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>CU04CUX42 Apertura</t>
+          <t>TR02CUX12 Qué necesito</t>
         </is>
       </c>
       <c r="B505" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C505" s="6" t="n">
-        <v>2.873073364886063e-05</v>
+        <v>2.825188808804629e-05</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t xml:space="preserve">TR04CUX32  Errores en pasaporte </t>
+          <t xml:space="preserve">Más información | Certificado de residencia precaria </t>
         </is>
       </c>
       <c r="B506" s="5" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C506" s="6" t="n">
-        <v>2.873073364886063e-05</v>
+        <v>2.825188808804629e-05</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>AM04CUX03 Apertura</t>
+          <t>TR03CUX05 Biblioteca Docente</t>
         </is>
       </c>
       <c r="B507" s="5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C507" s="6" t="n">
-        <v>2.873073364886063e-05</v>
+        <v>2.777304252723195e-05</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>TU03CUX03 Apertura</t>
+          <t>SA07CUX01 VIH</t>
         </is>
       </c>
       <c r="B508" s="5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C508" s="6" t="n">
-        <v>2.873073364886063e-05</v>
+        <v>2.777304252723195e-05</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t xml:space="preserve">Más información | Certificado de residencia precaria </t>
+          <t>TR03CUX25 Terminales de pago</t>
         </is>
       </c>
       <c r="B509" s="5" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C509" s="6" t="n">
-        <v>2.825188808804629e-05</v>
+        <v>2.777304252723195e-05</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>TR03CUX25 Terminales de pago</t>
+          <t>TR02CUX09 Qué necesito</t>
         </is>
       </c>
       <c r="B510" s="5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C510" s="6" t="n">
-        <v>2.777304252723195e-05</v>
+        <v>2.72941969664176e-05</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>SA07CUX01 VIH</t>
+          <t>Contingencia - Festividades</t>
         </is>
       </c>
       <c r="B511" s="5" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C511" s="6" t="n">
-        <v>2.777304252723195e-05</v>
+        <v>2.72941969664176e-05</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>Contingencia - Festividades</t>
+          <t>AM04CUX03 Apertura</t>
         </is>
       </c>
       <c r="B512" s="5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C512" s="6" t="n">
-        <v>2.72941969664176e-05</v>
+        <v>2.681535140560326e-05</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>GE02CUX02 Historia del 8M</t>
+          <t>Comida</t>
         </is>
       </c>
       <c r="B513" s="5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C513" s="6" t="n">
-        <v>2.72941969664176e-05</v>
+        <v>2.681535140560326e-05</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>TR02CUX09 Qué necesito</t>
+          <t>GE02CUX02 Historia del 8M</t>
         </is>
       </c>
       <c r="B514" s="5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C514" s="6" t="n">
-        <v>2.72941969664176e-05</v>
+        <v>2.681535140560326e-05</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>Comida</t>
+          <t>SA16CUX02 Quiero vacunarme</t>
         </is>
       </c>
       <c r="B515" s="5" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C515" s="6" t="n">
-        <v>2.681535140560326e-05</v>
+        <v>2.585766028397457e-05</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>TR03CUX05 Biblioteca Docente</t>
+          <t>TU01CUX15 Apertura</t>
         </is>
       </c>
       <c r="B516" s="5" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C516" s="6" t="n">
-        <v>2.681535140560326e-05</v>
+        <v>2.537881472316023e-05</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>TR02CUX12 Qué necesito</t>
+          <t>GA03CUX03 Apertura</t>
         </is>
       </c>
       <c r="B517" s="5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C517" s="6" t="n">
-        <v>2.585766028397457e-05</v>
+        <v>2.537881472316023e-05</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>TR03CUX03 Subsidios</t>
+          <t>TR01CUX04  Apertura</t>
         </is>
       </c>
       <c r="B518" s="5" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C518" s="6" t="n">
-        <v>2.537881472316023e-05</v>
+        <v>2.489996916234588e-05</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>TU01CUX15 Apertura</t>
+          <t>CU08CUX01  Apertura de contingencia II</t>
         </is>
       </c>
       <c r="B519" s="5" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C519" s="6" t="n">
-        <v>2.537881472316023e-05</v>
+        <v>2.394227804071719e-05</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>SA16CUX02 Quiero vacunarme</t>
+          <t>¿Quienes son tus creadores?</t>
         </is>
       </c>
       <c r="B520" s="5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C520" s="6" t="n">
-        <v>2.489996916234588e-05</v>
+        <v>2.394227804071719e-05</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>GA03CUX03 Apertura</t>
+          <t>JU03CUX01 Apertura</t>
         </is>
       </c>
       <c r="B521" s="5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C521" s="6" t="n">
-        <v>2.489996916234588e-05</v>
+        <v>2.394227804071719e-05</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>JU03CUX01 Apertura</t>
+          <t>TU03CUX05 Apertura</t>
         </is>
       </c>
       <c r="B522" s="5" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C522" s="6" t="n">
-        <v>2.489996916234588e-05</v>
+        <v>2.346343247990285e-05</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>CU02CUX01 Apertura</t>
+          <t>Código Postal por domicilio 2</t>
         </is>
       </c>
       <c r="B523" s="5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C523" s="6" t="n">
-        <v>2.489996916234588e-05</v>
+        <v>2.298458691908851e-05</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>TR01CUX04  Apertura</t>
+          <t>TR03CUX03 Subsidios</t>
         </is>
       </c>
       <c r="B524" s="5" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C524" s="6" t="n">
-        <v>2.489996916234588e-05</v>
+        <v>2.298458691908851e-05</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>CU08CUX01  Apertura de contingencia II</t>
+          <t>DH02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B525" s="5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C525" s="6" t="n">
-        <v>2.394227804071719e-05</v>
+        <v>2.298458691908851e-05</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>¿Quienes son tus creadores?</t>
+          <t>TR04CUX01 Apertura</t>
         </is>
       </c>
       <c r="B526" s="5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C526" s="6" t="n">
-        <v>2.394227804071719e-05</v>
+        <v>2.298458691908851e-05</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>DH05CUX01 Adicción al juego</t>
+          <t>TUR01CUX12 Preguntar género</t>
         </is>
       </c>
       <c r="B527" s="5" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C527" s="6" t="n">
-        <v>2.394227804071719e-05</v>
+        <v>2.250574135827416e-05</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>TU03CUX05 Apertura</t>
+          <t>TU03CUX07 Apertura</t>
         </is>
       </c>
       <c r="B528" s="5" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C528" s="6" t="n">
-        <v>2.346343247990285e-05</v>
+        <v>2.250574135827416e-05</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Código Postal por domicilio 2</t>
+          <t>DH05CUX01 Adicción al juego</t>
         </is>
       </c>
       <c r="B529" s="5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C529" s="6" t="n">
-        <v>2.298458691908851e-05</v>
+        <v>2.106920467583113e-05</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>TR04CUX01 Apertura</t>
+          <t>Servicios sociales</t>
         </is>
       </c>
       <c r="B530" s="5" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C530" s="6" t="n">
-        <v>2.298458691908851e-05</v>
+        <v>2.106920467583113e-05</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>TU03CUX07 Apertura</t>
+          <t>Autos Abandonados - Intentar más tarde</t>
         </is>
       </c>
       <c r="B531" s="5" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C531" s="6" t="n">
-        <v>2.250574135827416e-05</v>
+        <v>2.106920467583113e-05</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>DH02CUX01 Apertura</t>
+          <t>ED03CUX05 Profesorados</t>
         </is>
       </c>
       <c r="B532" s="5" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C532" s="6" t="n">
-        <v>2.202689579745982e-05</v>
+        <v>2.059035911501679e-05</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>BA Pyme</t>
+          <t>SA08CUX01 Apertura</t>
         </is>
       </c>
       <c r="B533" s="5" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C533" s="6" t="n">
-        <v>2.106920467583113e-05</v>
+        <v>2.059035911501679e-05</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>Servicios sociales</t>
+          <t>TR01CUX03  Apertura</t>
         </is>
       </c>
       <c r="B534" s="5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C534" s="6" t="n">
-        <v>2.106920467583113e-05</v>
+        <v>2.011151355420244e-05</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>Autos Abandonados - Intentar más tarde</t>
+          <t>AM04CUX06 Apertura</t>
         </is>
       </c>
       <c r="B535" s="5" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C535" s="6" t="n">
-        <v>2.106920467583113e-05</v>
+        <v>2.011151355420244e-05</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>TR01CUX03  Apertura</t>
+          <t>CU02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B536" s="5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C536" s="6" t="n">
-        <v>2.059035911501679e-05</v>
+        <v>2.011151355420244e-05</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>AM04CUX06 Apertura</t>
+          <t>JU02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B537" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C537" s="6" t="n">
-        <v>2.011151355420244e-05</v>
+        <v>1.96326679933881e-05</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>TR01CUX01 Apertura</t>
+          <t>Clausura obra o local</t>
         </is>
       </c>
       <c r="B538" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C538" s="6" t="n">
-        <v>2.011151355420244e-05</v>
+        <v>1.96326679933881e-05</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>JU02CUX01 Apertura</t>
+          <t>TR01CUX01 Apertura</t>
         </is>
       </c>
       <c r="B539" s="5" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C539" s="6" t="n">
-        <v>2.011151355420244e-05</v>
+        <v>1.96326679933881e-05</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>Clausura obra o local</t>
+          <t>BA Pyme</t>
         </is>
       </c>
       <c r="B540" s="5" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C540" s="6" t="n">
-        <v>1.96326679933881e-05</v>
+        <v>1.915382243257376e-05</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t xml:space="preserve">Apertura | Certificado de residencia precaria </t>
+          <t>MO10CUX07 Apertura</t>
         </is>
       </c>
       <c r="B541" s="5" t="n">
@@ -7490,14 +7490,14 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>MO10CUX07 Apertura</t>
+          <t xml:space="preserve">Apertura | Certificado de residencia precaria </t>
         </is>
       </c>
       <c r="B542" s="5" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C542" s="6" t="n">
-        <v>1.819613131094507e-05</v>
+        <v>1.915382243257376e-05</v>
       </c>
     </row>
     <row r="543">
@@ -7516,14 +7516,14 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>MO09CUX04 Apertura</t>
+          <t>DH11CUX08 Introducción</t>
         </is>
       </c>
       <c r="B544" s="5" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C544" s="6" t="n">
-        <v>1.819613131094507e-05</v>
+        <v>1.771728575013072e-05</v>
       </c>
     </row>
     <row r="545">
@@ -7533,16 +7533,16 @@
         </is>
       </c>
       <c r="B545" s="5" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C545" s="6" t="n">
-        <v>1.723844018931638e-05</v>
+        <v>1.771728575013072e-05</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>ED03CUX05 Profesorados</t>
+          <t>CU04CUX19 Apertura de contingencia</t>
         </is>
       </c>
       <c r="B546" s="5" t="n">
@@ -7555,7 +7555,7 @@
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>SA08CUX01 Apertura</t>
+          <t xml:space="preserve">MO05CUX13 Apertura </t>
         </is>
       </c>
       <c r="B547" s="5" t="n">
@@ -7568,20 +7568,20 @@
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>CU04CUX19 Apertura de contingencia</t>
+          <t>TR03CUX08 Habilitaciones</t>
         </is>
       </c>
       <c r="B548" s="5" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C548" s="6" t="n">
-        <v>1.723844018931638e-05</v>
+        <v>1.675959462850204e-05</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>GA01CUX01 Mercados</t>
+          <t>EDU04CUX01 CEC</t>
         </is>
       </c>
       <c r="B549" s="5" t="n">
@@ -7594,7 +7594,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>EDU04CUX01 CEC</t>
+          <t>MO09CUX04 Apertura</t>
         </is>
       </c>
       <c r="B550" s="5" t="n">
@@ -7607,20 +7607,20 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>CU01CUX16 Apertura (post-evento)</t>
+          <t>TR02CUX14 Nacimiento</t>
         </is>
       </c>
       <c r="B551" s="5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C551" s="6" t="n">
-        <v>1.628074906768769e-05</v>
+        <v>1.675959462850204e-05</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>Última Pregunta | Búsqueda de Farmacias</t>
+          <t>CU01CUX16 Apertura (post-evento)</t>
         </is>
       </c>
       <c r="B552" s="5" t="n">
@@ -7633,7 +7633,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>DH11CUX04 Apertura</t>
+          <t>Última Pregunta | Búsqueda de Farmacias</t>
         </is>
       </c>
       <c r="B553" s="5" t="n">
@@ -7646,7 +7646,7 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>CU10CUX02 Clemente</t>
+          <t>DH11CUX04 Apertura</t>
         </is>
       </c>
       <c r="B554" s="5" t="n">
@@ -7659,7 +7659,7 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>TR05CUX04 No figura en el registro</t>
+          <t>TR04CUX16 Apertura</t>
         </is>
       </c>
       <c r="B555" s="5" t="n">
@@ -7672,20 +7672,20 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>BX02CUX01 Pregunta 1</t>
+          <t>TR03CUX08 Seguridad alimentaria</t>
         </is>
       </c>
       <c r="B556" s="5" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C556" s="6" t="n">
-        <v>1.5323057946059e-05</v>
+        <v>1.484421238524466e-05</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>TR03CUX08 Seguridad alimentaria</t>
+          <t>CUL01CUX03 Apertura</t>
         </is>
       </c>
       <c r="B557" s="5" t="n">
@@ -7698,7 +7698,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>TR03CUX08 Habilitaciones</t>
+          <t>Realizar búsqueda de Código Postal por domicilio</t>
         </is>
       </c>
       <c r="B558" s="5" t="n">
@@ -7711,7 +7711,7 @@
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>CUL01CUX03 Apertura</t>
+          <t>GA01CUX01 Mercados</t>
         </is>
       </c>
       <c r="B559" s="5" t="n">
@@ -7724,20 +7724,20 @@
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>TR03CUX09 Denuncia vinculada con residuos patológicos</t>
+          <t>BX02CUX01 Pregunta 1</t>
         </is>
       </c>
       <c r="B560" s="5" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C560" s="6" t="n">
-        <v>1.436536682443032e-05</v>
+        <v>1.484421238524466e-05</v>
       </c>
     </row>
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>TR04CUX16 Apertura</t>
+          <t>TR03CUX09 Denuncia vinculada con residuos patológicos</t>
         </is>
       </c>
       <c r="B561" s="5" t="n">
@@ -7750,7 +7750,7 @@
     <row r="562">
       <c r="A562" t="inlineStr">
         <is>
-          <t>SA01CUX06  Apertura corta</t>
+          <t>EDU04CUX02 Apertura</t>
         </is>
       </c>
       <c r="B562" s="5" t="n">
@@ -7763,7 +7763,7 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>TR02CUX07 Apertura</t>
+          <t>SA01CUX06  Apertura corta</t>
         </is>
       </c>
       <c r="B563" s="5" t="n">
@@ -7776,7 +7776,7 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>EDU04CUX02 Apertura</t>
+          <t>TR02CUX07 Apertura</t>
         </is>
       </c>
       <c r="B564" s="5" t="n">
@@ -7789,20 +7789,20 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t xml:space="preserve">MO05CUX13 Apertura </t>
+          <t>TR05CUX04 No figura en el registro</t>
         </is>
       </c>
       <c r="B565" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C565" s="6" t="n">
-        <v>1.340767570280163e-05</v>
+        <v>1.388652126361597e-05</v>
       </c>
     </row>
     <row r="566">
       <c r="A566" t="inlineStr">
         <is>
-          <t>DH11CUX08 Introducción</t>
+          <t>CU01CUX15 Apertura Experiencia Interactiva</t>
         </is>
       </c>
       <c r="B566" s="5" t="n">
@@ -7815,20 +7815,20 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>CU01CUX15 Apertura Experiencia Interactiva</t>
+          <t>CU10CUX02 Clemente</t>
         </is>
       </c>
       <c r="B567" s="5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C567" s="6" t="n">
-        <v>1.292883014198729e-05</v>
+        <v>1.340767570280163e-05</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>Realizar búsqueda de Código Postal por domicilio</t>
+          <t>Hacer una consulta - Trámites Rúbrica</t>
         </is>
       </c>
       <c r="B568" s="5" t="n">
@@ -7854,20 +7854,20 @@
     <row r="570">
       <c r="A570" t="inlineStr">
         <is>
-          <t>Hacer una consulta - Trámites Rúbrica</t>
+          <t>¿Eres gay?</t>
         </is>
       </c>
       <c r="B570" s="5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C570" s="6" t="n">
-        <v>1.292883014198729e-05</v>
+        <v>1.244998458117294e-05</v>
       </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
         <is>
-          <t>GA01CUX01 Patios</t>
+          <t>AMC04CUX04 Público general</t>
         </is>
       </c>
       <c r="B571" s="5" t="n">
@@ -7880,7 +7880,7 @@
     <row r="572">
       <c r="A572" t="inlineStr">
         <is>
-          <t>ED04CUX17 Cómo funciona</t>
+          <t>GA01CUX01 Patios</t>
         </is>
       </c>
       <c r="B572" s="5" t="n">
@@ -7893,7 +7893,7 @@
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>AMC04CUX04 Público general</t>
+          <t>ED04CUX17 Cómo funciona</t>
         </is>
       </c>
       <c r="B573" s="5" t="n">
@@ -7906,20 +7906,20 @@
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>¿Eres gay?</t>
+          <t>CU10CUX02 Esquina Mafalda</t>
         </is>
       </c>
       <c r="B574" s="5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C574" s="6" t="n">
-        <v>1.244998458117294e-05</v>
+        <v>1.19711390203586e-05</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>CIU02CUX00 Superapertura</t>
+          <t>MO02CUX01 Apertura web</t>
         </is>
       </c>
       <c r="B575" s="5" t="n">
@@ -7932,7 +7932,7 @@
     <row r="576">
       <c r="A576" t="inlineStr">
         <is>
-          <t>DE05CUX02 Dónde se hacen</t>
+          <t>CIU02CUX00 Superapertura</t>
         </is>
       </c>
       <c r="B576" s="5" t="n">
@@ -7958,7 +7958,7 @@
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>CU01CUX02 MALBA</t>
+          <t>Código Postal por ubicación actual 2</t>
         </is>
       </c>
       <c r="B578" s="5" t="n">
@@ -7971,20 +7971,20 @@
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>AI Otorgamiento</t>
+          <t>DDHH03CUX01 Superapertura</t>
         </is>
       </c>
       <c r="B579" s="5" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C579" s="6" t="n">
-        <v>1.149229345954425e-05</v>
+        <v>1.101344789872991e-05</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="inlineStr">
         <is>
-          <t>DDHH03CUX01 Superapertura</t>
+          <t>SUA01CUX26 Apertura</t>
         </is>
       </c>
       <c r="B580" s="5" t="n">
@@ -7997,7 +7997,7 @@
     <row r="581">
       <c r="A581" t="inlineStr">
         <is>
-          <t>Coronavirus y gente de más de 70 (Apertura)  &gt; Hacer las compras * Apertura</t>
+          <t>CU01CUX14 Quiero ir</t>
         </is>
       </c>
       <c r="B581" s="5" t="n">
@@ -8010,7 +8010,7 @@
     <row r="582">
       <c r="A582" t="inlineStr">
         <is>
-          <t>MO05CUX03 Cómo hacerlo</t>
+          <t>CIU05CUX12 Envío exitoso</t>
         </is>
       </c>
       <c r="B582" s="5" t="n">
@@ -8023,46 +8023,46 @@
     <row r="583">
       <c r="A583" t="inlineStr">
         <is>
-          <t>SUA01CUX26 Apertura</t>
+          <t>Coronavirus y gente de más de 70 (Apertura)  &gt; Hacer las compras * Apertura</t>
         </is>
       </c>
       <c r="B583" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C583" s="6" t="n">
-        <v>1.053460233791557e-05</v>
+        <v>1.101344789872991e-05</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
         <is>
-          <t>Código Postal por ubicación actual 2</t>
+          <t>CU01CUX02 MALBA</t>
         </is>
       </c>
       <c r="B584" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C584" s="6" t="n">
-        <v>1.053460233791557e-05</v>
+        <v>1.101344789872991e-05</v>
       </c>
     </row>
     <row r="585">
       <c r="A585" t="inlineStr">
         <is>
-          <t>CU10CUX02 Esquina Mafalda</t>
+          <t>AI Otorgamiento</t>
         </is>
       </c>
       <c r="B585" s="5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C585" s="6" t="n">
-        <v>1.053460233791557e-05</v>
+        <v>1.101344789872991e-05</v>
       </c>
     </row>
     <row r="586">
       <c r="A586" t="inlineStr">
         <is>
-          <t>Registro de artistas callejeros (Apertura)</t>
+          <t>Pasaporte Covid | Revisar datos | Persistir info</t>
         </is>
       </c>
       <c r="B586" s="5" t="n">
@@ -8075,7 +8075,7 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>DH11CUX08 Video 1</t>
+          <t>Registro de artistas callejeros (Apertura)</t>
         </is>
       </c>
       <c r="B587" s="5" t="n">
@@ -8088,14 +8088,14 @@
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>Pasaporte Covid | Revisar datos | Persistir info</t>
+          <t>Llamá gratis al 144</t>
         </is>
       </c>
       <c r="B588" s="5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C588" s="6" t="n">
-        <v>1.053460233791557e-05</v>
+        <v>1.005575677710122e-05</v>
       </c>
     </row>
     <row r="589">
@@ -8114,7 +8114,7 @@
     <row r="590">
       <c r="A590" t="inlineStr">
         <is>
-          <t>Llamá gratis al 144</t>
+          <t>CU09CUX01 Apertura</t>
         </is>
       </c>
       <c r="B590" s="5" t="n">
@@ -8127,7 +8127,7 @@
     <row r="591">
       <c r="A591" t="inlineStr">
         <is>
-          <t>EDU04CUX28 Apertura</t>
+          <t>GE03CUX03 Apertura</t>
         </is>
       </c>
       <c r="B591" s="5" t="n">
@@ -8140,7 +8140,7 @@
     <row r="592">
       <c r="A592" t="inlineStr">
         <is>
-          <t>DDHH03CUX05 Apertura</t>
+          <t>EDU04CUX28 Apertura</t>
         </is>
       </c>
       <c r="B592" s="5" t="n">
@@ -8153,7 +8153,7 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>GE03CUX03 Apertura</t>
+          <t>CU10CUX02 La Jirafa</t>
         </is>
       </c>
       <c r="B593" s="5" t="n">
@@ -8192,7 +8192,7 @@
     <row r="596">
       <c r="A596" t="inlineStr">
         <is>
-          <t>CU10CUX02 La Jirafa</t>
+          <t>DDHH03CUX05 Apertura</t>
         </is>
       </c>
       <c r="B596" s="5" t="n">
@@ -8205,33 +8205,33 @@
     <row r="597">
       <c r="A597" t="inlineStr">
         <is>
-          <t>Validación Audios - Falla en el servicio</t>
+          <t>MO05CUX03 Cómo hacerlo</t>
         </is>
       </c>
       <c r="B597" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C597" s="6" t="n">
-        <v>8.61922009465819e-06</v>
+        <v>9.098065655472534e-06</v>
       </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
         <is>
-          <t>SE01CUX06 Apertura</t>
+          <t>Dónde hacerlo | Certificación de firmas</t>
         </is>
       </c>
       <c r="B598" s="5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C598" s="6" t="n">
-        <v>8.61922009465819e-06</v>
+        <v>9.098065655472534e-06</v>
       </c>
     </row>
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>CU04CUX16 Apertura contingencia</t>
+          <t>Qué necesito | Identificación Tardía</t>
         </is>
       </c>
       <c r="B599" s="5" t="n">
@@ -8244,7 +8244,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>Qué necesito | Identificación Tardía</t>
+          <t>SE01CUX06 Apertura</t>
         </is>
       </c>
       <c r="B600" s="5" t="n">
@@ -8257,33 +8257,33 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>CO08CUX06 Apertura</t>
+          <t>CU04CUX16 Apertura contingencia</t>
         </is>
       </c>
       <c r="B601" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C601" s="6" t="n">
-        <v>8.140374533843846e-06</v>
+        <v>8.61922009465819e-06</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="inlineStr">
         <is>
-          <t>SA01CUX07 - Formulario para declarar vacuna</t>
+          <t>Validación Audios - Falla en el servicio</t>
         </is>
       </c>
       <c r="B602" s="5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C602" s="6" t="n">
-        <v>8.140374533843846e-06</v>
+        <v>8.61922009465819e-06</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="inlineStr">
         <is>
-          <t>SUA01CUX27 Dónde ubicar la luminaria</t>
+          <t>CO08CUX06 Apertura</t>
         </is>
       </c>
       <c r="B603" s="5" t="n">
@@ -8296,7 +8296,7 @@
     <row r="604">
       <c r="A604" t="inlineStr">
         <is>
-          <t>CU10CUX02 Mafalda y sus amigos</t>
+          <t>SA01CUX07 - Formulario para declarar vacuna</t>
         </is>
       </c>
       <c r="B604" s="5" t="n">
@@ -8313,16 +8313,16 @@
         </is>
       </c>
       <c r="B605" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C605" s="6" t="n">
-        <v>7.661528973029502e-06</v>
+        <v>8.140374533843846e-06</v>
       </c>
     </row>
     <row r="606">
       <c r="A606" t="inlineStr">
         <is>
-          <t>DH011CUX02 Presencial</t>
+          <t>Costos del trámite | Disolución de Unión Civil / Convivencial</t>
         </is>
       </c>
       <c r="B606" s="5" t="n">
@@ -8335,7 +8335,7 @@
     <row r="607">
       <c r="A607" t="inlineStr">
         <is>
-          <t>Dónde lo hago | Identificación Tardía</t>
+          <t>DH011CUX02 Presencial</t>
         </is>
       </c>
       <c r="B607" s="5" t="n">
@@ -8348,20 +8348,20 @@
     <row r="608">
       <c r="A608" t="inlineStr">
         <is>
-          <t>Costos del trámite | Disolución de Unión Civil / Convivencial</t>
+          <t>DE05CUX02 Dónde se hacen</t>
         </is>
       </c>
       <c r="B608" s="5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C608" s="6" t="n">
-        <v>7.661528973029502e-06</v>
+        <v>7.182683412215158e-06</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>TR03CUX16 Denuncia a administradores de consorcio</t>
+          <t>CU10CUX02 Mafalda y sus amigos</t>
         </is>
       </c>
       <c r="B609" s="5" t="n">
@@ -8374,7 +8374,7 @@
     <row r="610">
       <c r="A610" t="inlineStr">
         <is>
-          <t xml:space="preserve">​​DH05CUX01 Más teléfonos​ </t>
+          <t>Mitre -Viaductos-</t>
         </is>
       </c>
       <c r="B610" s="5" t="n">
@@ -8387,7 +8387,7 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDU04CUX30 Adolescencia </t>
+          <t xml:space="preserve">​​DH05CUX01 Más teléfonos​ </t>
         </is>
       </c>
       <c r="B611" s="5" t="n">
@@ -8400,46 +8400,46 @@
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>CU11CUX02 Qué propuestas hay</t>
+          <t>EP04CUX01 Apertura sin registro contingencia</t>
         </is>
       </c>
       <c r="B612" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C612" s="6" t="n">
-        <v>7.182683412215158e-06</v>
+        <v>6.703837851400815e-06</v>
       </c>
     </row>
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>Dónde hacerlo | Certificación de firmas</t>
+          <t>AM04CUX05 Quiero ir</t>
         </is>
       </c>
       <c r="B613" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C613" s="6" t="n">
-        <v>7.182683412215158e-06</v>
+        <v>6.703837851400815e-06</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
         <is>
-          <t>Mitre -Viaductos-</t>
+          <t>CU08CUX02 Cuidados del calor</t>
         </is>
       </c>
       <c r="B614" s="5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C614" s="6" t="n">
-        <v>7.182683412215158e-06</v>
+        <v>6.703837851400815e-06</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>Noviazgo</t>
+          <t>TU01CUX02 Turismo en Boti</t>
         </is>
       </c>
       <c r="B615" s="5" t="n">
@@ -8452,7 +8452,7 @@
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>CU08CUX02 Cuidados del calor</t>
+          <t>Noviazgo</t>
         </is>
       </c>
       <c r="B616" s="5" t="n">
@@ -8465,46 +8465,46 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>EP04CUX01 Apertura web</t>
+          <t>CU01CUX02 Colón Fábrica</t>
         </is>
       </c>
       <c r="B617" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C617" s="6" t="n">
-        <v>6.703837851400815e-06</v>
+        <v>6.224992290586471e-06</v>
       </c>
     </row>
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>AGC01CUX00 Chatear con alguien</t>
+          <t>SA18CUX01 Apertura</t>
         </is>
       </c>
       <c r="B618" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C618" s="6" t="n">
-        <v>6.703837851400815e-06</v>
+        <v>6.224992290586471e-06</v>
       </c>
     </row>
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>TU01CUX02 Turismo en Boti</t>
+          <t>SUA01CUX011 Imagen - Error de formato, tamaño o peso - Extracción de árbol</t>
         </is>
       </c>
       <c r="B619" s="5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C619" s="6" t="n">
-        <v>6.703837851400815e-06</v>
+        <v>6.224992290586471e-06</v>
       </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>CIU05CUX01 Apertura</t>
+          <t xml:space="preserve">EDU04CUX30 Adolescencia </t>
         </is>
       </c>
       <c r="B620" s="5" t="n">
@@ -8517,85 +8517,85 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>SA18CUX01 Apertura</t>
+          <t>Agradecimiento gestión</t>
         </is>
       </c>
       <c r="B621" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C621" s="6" t="n">
-        <v>6.224992290586471e-06</v>
+        <v>5.746146729772127e-06</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>Mostrar Resultados | Ecobici</t>
+          <t>CU11CUX02 Qué propuestas hay</t>
         </is>
       </c>
       <c r="B622" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C622" s="6" t="n">
-        <v>6.224992290586471e-06</v>
+        <v>5.746146729772127e-06</v>
       </c>
     </row>
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>SUA01CUX011 Imagen - Error de formato, tamaño o peso - Extracción de árbol</t>
+          <t>DE03CUX02 Quiero hacer deporte</t>
         </is>
       </c>
       <c r="B623" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C623" s="6" t="n">
-        <v>6.224992290586471e-06</v>
+        <v>5.746146729772127e-06</v>
       </c>
     </row>
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>EP04CUX01 Apertura sin registro contingencia</t>
+          <t>CIU05CUX01 Apertura</t>
         </is>
       </c>
       <c r="B624" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C624" s="6" t="n">
-        <v>6.224992290586471e-06</v>
+        <v>5.746146729772127e-06</v>
       </c>
     </row>
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>CU09CUX01 Apertura</t>
+          <t>Situación de calle</t>
         </is>
       </c>
       <c r="B625" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C625" s="6" t="n">
-        <v>6.224992290586471e-06</v>
+        <v>5.746146729772127e-06</v>
       </c>
     </row>
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>CU01CUX02 Colón Fábrica</t>
+          <t>Salir de la experiencia</t>
         </is>
       </c>
       <c r="B626" s="5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C626" s="6" t="n">
-        <v>6.224992290586471e-06</v>
+        <v>5.746146729772127e-06</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>Situación de calle</t>
+          <t>NI02CUX01 Tiempo libre</t>
         </is>
       </c>
       <c r="B627" s="5" t="n">
@@ -8608,7 +8608,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>Salir de la experiencia</t>
+          <t>CU10CUX02 Apertura Mafalda</t>
         </is>
       </c>
       <c r="B628" s="5" t="n">
@@ -8621,7 +8621,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>Agradecimiento gestión</t>
+          <t>Dónde hacerlo | Certificado de Pobreza</t>
         </is>
       </c>
       <c r="B629" s="5" t="n">
@@ -8634,7 +8634,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>NI02CUX01 Tiempo libre</t>
+          <t>EP04CUX01 Apertura web</t>
         </is>
       </c>
       <c r="B630" s="5" t="n">
@@ -8647,7 +8647,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>DH11CUX08 Apertura</t>
+          <t>CIU05CUX07 Apertura QR</t>
         </is>
       </c>
       <c r="B631" s="5" t="n">
@@ -8660,7 +8660,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>MO05CUX12 Cómo es el trámite</t>
+          <t>TR03CUX06 Servicios de salud para la prevención de zoonosis</t>
         </is>
       </c>
       <c r="B632" s="5" t="n">
@@ -8686,7 +8686,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>MO02CUX01 Apertura web</t>
+          <t>DH11CUX08 Video 1</t>
         </is>
       </c>
       <c r="B634" s="5" t="n">
@@ -8699,7 +8699,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>CIU05CUX07 Apertura QR</t>
+          <t>CU01CUX07 Apertura</t>
         </is>
       </c>
       <c r="B635" s="5" t="n">
@@ -8712,20 +8712,20 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>EDU05CUX05 Inglés</t>
+          <t>TR03CUX09 Apertura</t>
         </is>
       </c>
       <c r="B636" s="5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C636" s="6" t="n">
-        <v>5.746146729772127e-06</v>
+        <v>5.267301168957783e-06</v>
       </c>
     </row>
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>Respuestas TXT Gen</t>
+          <t>DH11CUX03 Apertura QR keywords</t>
         </is>
       </c>
       <c r="B637" s="5" t="n">
@@ -8738,7 +8738,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>CU10CUX02 Apertura Mafalda</t>
+          <t>¿Hombre o Mujer?</t>
         </is>
       </c>
       <c r="B638" s="5" t="n">
@@ -8764,7 +8764,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>TR03CUX09 Apertura</t>
+          <t>01. CIU02CUX01 - Comunas de la Ciudad</t>
         </is>
       </c>
       <c r="B640" s="5" t="n">
@@ -8777,7 +8777,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>AM04CUX05 Quiero ir</t>
+          <t>Respuestas TXT Gen</t>
         </is>
       </c>
       <c r="B641" s="5" t="n">
@@ -8790,7 +8790,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>Realizar búsqueda de Código Postal por ubicación desde variable auxiliar</t>
+          <t>CO08CUX07 Apertura</t>
         </is>
       </c>
       <c r="B642" s="5" t="n">
@@ -8803,33 +8803,33 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>¿Hombre o Mujer?</t>
+          <t>Dónde lo hago | Identificación Tardía</t>
         </is>
       </c>
       <c r="B643" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C643" s="6" t="n">
-        <v>5.267301168957783e-06</v>
+        <v>4.788455608143439e-06</v>
       </c>
     </row>
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>01. CIU02CUX01 - Comunas de la Ciudad</t>
+          <t>DH10CUX01 Clave fiscal</t>
         </is>
       </c>
       <c r="B644" s="5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C644" s="6" t="n">
-        <v>5.267301168957783e-06</v>
+        <v>4.788455608143439e-06</v>
       </c>
     </row>
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>CO08CUX07 Apertura</t>
+          <t>MO09CUX04 Cortes y desvíos</t>
         </is>
       </c>
       <c r="B645" s="5" t="n">
@@ -8842,7 +8842,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>DH10CUX01 Clave fiscal</t>
+          <t xml:space="preserve">Bicicletero - Buscar por ubicacion </t>
         </is>
       </c>
       <c r="B646" s="5" t="n">
@@ -8855,7 +8855,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>NI01CUX09 Inicio del cuento</t>
+          <t>Resolver Ubicación Domicilio | Baches</t>
         </is>
       </c>
       <c r="B647" s="5" t="n">
@@ -8868,7 +8868,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>Dónde hacerlo | Certificado de Pobreza</t>
+          <t xml:space="preserve">Antecedentes penales | Certificado de residencia precaria </t>
         </is>
       </c>
       <c r="B648" s="5" t="n">
@@ -8881,7 +8881,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t xml:space="preserve">Antecedentes penales | Certificado de residencia precaria </t>
+          <t>DEC05CUX02 Apertura</t>
         </is>
       </c>
       <c r="B649" s="5" t="n">
@@ -8894,27 +8894,27 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bicicletero - Buscar por ubicacion </t>
+          <t>¿Bien, vos?</t>
         </is>
       </c>
       <c r="B650" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C650" s="6" t="n">
-        <v>4.788455608143439e-06</v>
+        <v>4.309610047329095e-06</v>
       </c>
     </row>
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>Resolver Ubicación Domicilio | Baches</t>
+          <t>EDU05CUX05 Inglés</t>
         </is>
       </c>
       <c r="B651" s="5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C651" s="6" t="n">
-        <v>4.788455608143439e-06</v>
+        <v>4.309610047329095e-06</v>
       </c>
     </row>
     <row r="652">
@@ -8946,7 +8946,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>CU01CUX07 Apertura</t>
+          <t>Mostrar Resultados | Ecobici</t>
         </is>
       </c>
       <c r="B654" s="5" t="n">
@@ -8959,7 +8959,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>¿Bien, vos?</t>
+          <t>NI01CUX09 Inicio del cuento</t>
         </is>
       </c>
       <c r="B655" s="5" t="n">
@@ -8972,7 +8972,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>AC02CUX04 SAME</t>
+          <t>Ver otra dirección de permitido estacionar</t>
         </is>
       </c>
       <c r="B656" s="5" t="n">
@@ -8985,7 +8985,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>Ver otra dirección de permitido estacionar</t>
+          <t>SUA01CUX27 Dónde ubicar la luminaria</t>
         </is>
       </c>
       <c r="B657" s="5" t="n">
@@ -9011,33 +9011,33 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>MO11CUX01 Trambús</t>
+          <t>CIU05CUX08 Sitios históricos Belgrano</t>
         </is>
       </c>
       <c r="B659" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C659" s="6" t="n">
-        <v>4.309610047329095e-06</v>
+        <v>3.830764486514751e-06</v>
       </c>
     </row>
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>DEC05CUX02 Apertura</t>
+          <t>DH11CUX08 Apertura</t>
         </is>
       </c>
       <c r="B660" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C660" s="6" t="n">
-        <v>4.309610047329095e-06</v>
+        <v>3.830764486514751e-06</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>CU01CUX14 Quiero ir</t>
+          <t>Respuesta de contexto</t>
         </is>
       </c>
       <c r="B661" s="5" t="n">
@@ -9050,7 +9050,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>San Martín -Viaductos-</t>
+          <t>Hablar con una persona derivado a WhatsApp</t>
         </is>
       </c>
       <c r="B662" s="5" t="n">
@@ -9063,7 +9063,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>GE03CUX02 TrabajoBA</t>
+          <t>SA08CUX02 Apertura</t>
         </is>
       </c>
       <c r="B663" s="5" t="n">
@@ -9076,7 +9076,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>MO09CUX04 Cortes y desvíos</t>
+          <t>San Martín -Viaductos-</t>
         </is>
       </c>
       <c r="B664" s="5" t="n">
@@ -9089,46 +9089,46 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>TR03CUX06 Servicios de salud para la prevención de zoonosis</t>
+          <t>fulfilled of Condición</t>
         </is>
       </c>
       <c r="B665" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C665" s="6" t="n">
-        <v>3.830764486514751e-06</v>
+        <v>3.351918925700407e-06</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Sitios históricos Belgrano</t>
+          <t>TR03CUX17 Certificado de recupero del vehículo fuera de término</t>
         </is>
       </c>
       <c r="B666" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C666" s="6" t="n">
-        <v>3.830764486514751e-06</v>
+        <v>3.351918925700407e-06</v>
       </c>
     </row>
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>Respuesta de contexto</t>
+          <t>Inactividad  del usuario: limpiar datos de sesión</t>
         </is>
       </c>
       <c r="B667" s="5" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C667" s="6" t="n">
-        <v>3.830764486514751e-06</v>
+        <v>3.351918925700407e-06</v>
       </c>
     </row>
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>TR03CUX17 Certificado de recupero del vehículo fuera de término</t>
+          <t>TU03CUX09 Qué hay para hacer</t>
         </is>
       </c>
       <c r="B668" s="5" t="n">
@@ -9154,7 +9154,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>Amistad</t>
+          <t>Realizar búsqueda de Código Postal por ubicación desde variable auxiliar</t>
         </is>
       </c>
       <c r="B670" s="5" t="n">
@@ -9167,7 +9167,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>SA08CUX02 Apertura</t>
+          <t>Amistad</t>
         </is>
       </c>
       <c r="B671" s="5" t="n">
@@ -9180,7 +9180,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>Qué necesito | Certificación de firmas</t>
+          <t>TR03CUX17 Apertura</t>
         </is>
       </c>
       <c r="B672" s="5" t="n">
@@ -9193,7 +9193,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>EM03CUX02 Cursos virtuales</t>
+          <t>Donde vive</t>
         </is>
       </c>
       <c r="B673" s="5" t="n">
@@ -9206,7 +9206,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>DH02CUX01 Capacitaciones</t>
+          <t>Qué necesito | Certificación de firmas</t>
         </is>
       </c>
       <c r="B674" s="5" t="n">
@@ -9219,85 +9219,85 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
-          <t>fulfilled of Condición</t>
+          <t xml:space="preserve"> SUA01CUX07 Cargar Foto 2 - Reparación de luminaria</t>
         </is>
       </c>
       <c r="B675" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C675" s="6" t="n">
-        <v>3.351918925700407e-06</v>
+        <v>2.873073364886063e-06</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>Hablar con una persona derivado a WhatsApp</t>
+          <t>TUR01CUX03 Validar datos</t>
         </is>
       </c>
       <c r="B676" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C676" s="6" t="n">
-        <v>3.351918925700407e-06</v>
+        <v>2.873073364886063e-06</v>
       </c>
     </row>
     <row r="677">
       <c r="A677" t="inlineStr">
         <is>
-          <t>TR03CUX17 Apertura</t>
+          <t>CU01CUX02 Palacio Noel</t>
         </is>
       </c>
       <c r="B677" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C677" s="6" t="n">
-        <v>3.351918925700407e-06</v>
+        <v>2.873073364886063e-06</v>
       </c>
     </row>
     <row r="678">
       <c r="A678" t="inlineStr">
         <is>
-          <t>Derivación Becas Alimentarias - ✅ Auxiliar disponible</t>
+          <t>TR03CUX16 Denuncia a administradores de consorcio</t>
         </is>
       </c>
       <c r="B678" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C678" s="6" t="n">
-        <v>3.351918925700407e-06</v>
+        <v>2.873073364886063e-06</v>
       </c>
     </row>
     <row r="679">
       <c r="A679" t="inlineStr">
         <is>
-          <t>Donde vive</t>
+          <t>TU03CUX06 Apertura</t>
         </is>
       </c>
       <c r="B679" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C679" s="6" t="n">
-        <v>3.351918925700407e-06</v>
+        <v>2.873073364886063e-06</v>
       </c>
     </row>
     <row r="680">
       <c r="A680" t="inlineStr">
         <is>
-          <t>Inactividad  del usuario: limpiar datos de sesión</t>
+          <t>SUA01CUX22 Apertura desratización en colegios</t>
         </is>
       </c>
       <c r="B680" s="5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C680" s="6" t="n">
-        <v>3.351918925700407e-06</v>
+        <v>2.873073364886063e-06</v>
       </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
         <is>
-          <t>EDU05CUX02 * Apertura</t>
+          <t>SUA01CUX20 Apertura</t>
         </is>
       </c>
       <c r="B681" s="5" t="n">
@@ -9310,7 +9310,7 @@
     <row r="682">
       <c r="A682" t="inlineStr">
         <is>
-          <t>SUA01CUX22 Apertura desratización en colegios</t>
+          <t>DH02CUX01 Capacitaciones</t>
         </is>
       </c>
       <c r="B682" s="5" t="n">
@@ -9336,7 +9336,7 @@
     <row r="684">
       <c r="A684" t="inlineStr">
         <is>
-          <t>TU03CUX06 Apertura</t>
+          <t>MO05CUX12 Cómo es el trámite</t>
         </is>
       </c>
       <c r="B684" s="5" t="n">
@@ -9349,7 +9349,7 @@
     <row r="685">
       <c r="A685" t="inlineStr">
         <is>
-          <t>DE03CUX02 Quiero hacer deporte</t>
+          <t>CU02CUX01 Teatro San Martín</t>
         </is>
       </c>
       <c r="B685" s="5" t="n">
@@ -9362,137 +9362,137 @@
     <row r="686">
       <c r="A686" t="inlineStr">
         <is>
-          <t>DH05CUX01 Apertura corta</t>
+          <t>Cómo hacerlo | Certificación de firmas</t>
         </is>
       </c>
       <c r="B686" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C686" s="6" t="n">
-        <v>2.873073364886063e-06</v>
+        <v>2.394227804071719e-06</v>
       </c>
     </row>
     <row r="687">
       <c r="A687" t="inlineStr">
         <is>
-          <t>TR02CUX01 Cómo pedirlo</t>
+          <t>JU03CUX01 Tengo una consulta</t>
         </is>
       </c>
       <c r="B687" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C687" s="6" t="n">
-        <v>2.873073364886063e-06</v>
+        <v>2.394227804071719e-06</v>
       </c>
     </row>
     <row r="688">
       <c r="A688" t="inlineStr">
         <is>
-          <t>SUA01CUX20 Apertura</t>
+          <t>Ubicación no encontrada | Ecobici</t>
         </is>
       </c>
       <c r="B688" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C688" s="6" t="n">
-        <v>2.873073364886063e-06</v>
+        <v>2.394227804071719e-06</v>
       </c>
     </row>
     <row r="689">
       <c r="A689" t="inlineStr">
         <is>
-          <t>CU01CUX07 Ciudades imaginadas</t>
+          <t>AM04CUX04 Dónde queda</t>
         </is>
       </c>
       <c r="B689" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C689" s="6" t="n">
-        <v>2.873073364886063e-06</v>
+        <v>2.394227804071719e-06</v>
       </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
         <is>
-          <t>DH11CUX03 Apertura QR keywords</t>
+          <t>AC02CUX04 SAME</t>
         </is>
       </c>
       <c r="B690" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C690" s="6" t="n">
-        <v>2.873073364886063e-06</v>
+        <v>2.394227804071719e-06</v>
       </c>
     </row>
     <row r="691">
       <c r="A691" t="inlineStr">
         <is>
-          <t>CU02CUX01 Teatro San Martín</t>
+          <t>Mostrar más Resultados | Ecobici</t>
         </is>
       </c>
       <c r="B691" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C691" s="6" t="n">
-        <v>2.873073364886063e-06</v>
+        <v>2.394227804071719e-06</v>
       </c>
     </row>
     <row r="692">
       <c r="A692" t="inlineStr">
         <is>
-          <t>CU01CUX02 Palacio Noel</t>
+          <t>Pasaporte Sanitario * Apertura &gt; Código QR</t>
         </is>
       </c>
       <c r="B692" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C692" s="6" t="n">
-        <v>2.873073364886063e-06</v>
+        <v>2.394227804071719e-06</v>
       </c>
     </row>
     <row r="693">
       <c r="A693" t="inlineStr">
         <is>
-          <t>PC03CUX01 Voluntarios BA</t>
+          <t>TR01CUX03 Cómo hacer el trámite</t>
         </is>
       </c>
       <c r="B693" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C693" s="6" t="n">
-        <v>2.873073364886063e-06</v>
+        <v>2.394227804071719e-06</v>
       </c>
     </row>
     <row r="694">
       <c r="A694" t="inlineStr">
         <is>
-          <t>SA08CUX01 Buscar hospitales</t>
+          <t xml:space="preserve">EDU04CUX30 Apertura </t>
         </is>
       </c>
       <c r="B694" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C694" s="6" t="n">
-        <v>2.873073364886063e-06</v>
+        <v>2.394227804071719e-06</v>
       </c>
     </row>
     <row r="695">
       <c r="A695" t="inlineStr">
         <is>
-          <t xml:space="preserve"> SUA01CUX07 Cargar Foto 2 - Reparación de luminaria</t>
+          <t>EDU04CUX30 Celu en el aula</t>
         </is>
       </c>
       <c r="B695" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C695" s="6" t="n">
-        <v>2.873073364886063e-06</v>
+        <v>2.394227804071719e-06</v>
       </c>
     </row>
     <row r="696">
       <c r="A696" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Elegir tipo de turrno</t>
+          <t>CU10CUX02 Isidoro Cañones</t>
         </is>
       </c>
       <c r="B696" s="5" t="n">
@@ -9505,7 +9505,7 @@
     <row r="697">
       <c r="A697" t="inlineStr">
         <is>
-          <t>CU04CUX48 Apertura</t>
+          <t>GE03CUX02 TrabajoBA</t>
         </is>
       </c>
       <c r="B697" s="5" t="n">
@@ -9518,7 +9518,7 @@
     <row r="698">
       <c r="A698" t="inlineStr">
         <is>
-          <t>Ubicación no encontrada | Ecobici</t>
+          <t>Centralizar rúbrica</t>
         </is>
       </c>
       <c r="B698" s="5" t="n">
@@ -9531,7 +9531,7 @@
     <row r="699">
       <c r="A699" t="inlineStr">
         <is>
-          <t>Pasaporte Sanitario * Apertura &gt; Código QR</t>
+          <t>EDU05CUX02 * Apertura</t>
         </is>
       </c>
       <c r="B699" s="5" t="n">
@@ -9544,7 +9544,7 @@
     <row r="700">
       <c r="A700" t="inlineStr">
         <is>
-          <t>DEC05CUX02 Cómo participo</t>
+          <t>Contento</t>
         </is>
       </c>
       <c r="B700" s="5" t="n">
@@ -9557,7 +9557,7 @@
     <row r="701">
       <c r="A701" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDU04CUX30 Apertura </t>
+          <t>AI Renovación</t>
         </is>
       </c>
       <c r="B701" s="5" t="n">
@@ -9570,72 +9570,72 @@
     <row r="702">
       <c r="A702" t="inlineStr">
         <is>
-          <t>Contento</t>
+          <t>¿De qué jugás?</t>
         </is>
       </c>
       <c r="B702" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C702" s="6" t="n">
-        <v>2.394227804071719e-06</v>
+        <v>1.915382243257376e-06</v>
       </c>
     </row>
     <row r="703">
       <c r="A703" t="inlineStr">
         <is>
-          <t>TR03CUX07 Apertura</t>
+          <t>¿Goku o Vegeta?</t>
         </is>
       </c>
       <c r="B703" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C703" s="6" t="n">
-        <v>2.394227804071719e-06</v>
+        <v>1.915382243257376e-06</v>
       </c>
     </row>
     <row r="704">
       <c r="A704" t="inlineStr">
         <is>
-          <t>TR01CUX03 Cómo hacer el trámite</t>
+          <t>¿Sos una máquina?</t>
         </is>
       </c>
       <c r="B704" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C704" s="6" t="n">
-        <v>2.394227804071719e-06</v>
+        <v>1.915382243257376e-06</v>
       </c>
     </row>
     <row r="705">
       <c r="A705" t="inlineStr">
         <is>
-          <t>Cómo hacerlo | Certificación de firmas</t>
+          <t xml:space="preserve">SE01CUX01 Proceso de Selección </t>
         </is>
       </c>
       <c r="B705" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C705" s="6" t="n">
-        <v>2.394227804071719e-06</v>
+        <v>1.915382243257376e-06</v>
       </c>
     </row>
     <row r="706">
       <c r="A706" t="inlineStr">
         <is>
-          <t>Centralizar rúbrica</t>
+          <t>DH02CUX01 Financiamiento</t>
         </is>
       </c>
       <c r="B706" s="5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C706" s="6" t="n">
-        <v>2.394227804071719e-06</v>
+        <v>1.915382243257376e-06</v>
       </c>
     </row>
     <row r="707">
       <c r="A707" t="inlineStr">
         <is>
-          <t>¿De qué jugás?</t>
+          <t>DDHH03CUX02 Quiero adoptar</t>
         </is>
       </c>
       <c r="B707" s="5" t="n">
@@ -9648,7 +9648,7 @@
     <row r="708">
       <c r="A708" t="inlineStr">
         <is>
-          <t>CU01CUX08 Apertura</t>
+          <t>SUA01CUX33 Apertura</t>
         </is>
       </c>
       <c r="B708" s="5" t="n">
@@ -9661,7 +9661,7 @@
     <row r="709">
       <c r="A709" t="inlineStr">
         <is>
-          <t>CO04CUX08 Apertura</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="B709" s="5" t="n">
@@ -9687,7 +9687,7 @@
     <row r="711">
       <c r="A711" t="inlineStr">
         <is>
-          <t>CU01CUX15 Comienzo - Cabras Pista 1</t>
+          <t>TR03CUX03 Apertura</t>
         </is>
       </c>
       <c r="B711" s="5" t="n">
@@ -9700,7 +9700,7 @@
     <row r="712">
       <c r="A712" t="inlineStr">
         <is>
-          <t>Derivación Becas Alimentarias - Fuera de horario de atención</t>
+          <t>MO10CUX01 Recorridos</t>
         </is>
       </c>
       <c r="B712" s="5" t="n">
@@ -9713,7 +9713,7 @@
     <row r="713">
       <c r="A713" t="inlineStr">
         <is>
-          <t>SUA01CUX33 Apertura</t>
+          <t>DH08CUX03  Apertura de contingencia II</t>
         </is>
       </c>
       <c r="B713" s="5" t="n">
@@ -9726,7 +9726,7 @@
     <row r="714">
       <c r="A714" t="inlineStr">
         <is>
-          <t>DH02CUX01 Financiamiento</t>
+          <t>CU01CUX10 Apertura</t>
         </is>
       </c>
       <c r="B714" s="5" t="n">
@@ -9739,7 +9739,7 @@
     <row r="715">
       <c r="A715" t="inlineStr">
         <is>
-          <t>GE03CUX02 Apertura</t>
+          <t>CU04CUX48 Apertura</t>
         </is>
       </c>
       <c r="B715" s="5" t="n">
@@ -9752,7 +9752,7 @@
     <row r="716">
       <c r="A716" t="inlineStr">
         <is>
-          <t>¿Goku o Vegeta?</t>
+          <t>CU01CUX08 Apertura</t>
         </is>
       </c>
       <c r="B716" s="5" t="n">
@@ -9765,7 +9765,7 @@
     <row r="717">
       <c r="A717" t="inlineStr">
         <is>
-          <t>¿Sos una máquina?</t>
+          <t>Levantamiento de clausura ascensor</t>
         </is>
       </c>
       <c r="B717" s="5" t="n">
@@ -9778,7 +9778,7 @@
     <row r="718">
       <c r="A718" t="inlineStr">
         <is>
-          <t>​​DH02CUX01 Apertura corta​</t>
+          <t>CIU05CUX08 Sitios Históricos La Boca</t>
         </is>
       </c>
       <c r="B718" s="5" t="n">
@@ -9791,7 +9791,7 @@
     <row r="719">
       <c r="A719" t="inlineStr">
         <is>
-          <t>AI Renovación</t>
+          <t>TU01CUX05  Necesito ayuda</t>
         </is>
       </c>
       <c r="B719" s="5" t="n">
@@ -9804,7 +9804,7 @@
     <row r="720">
       <c r="A720" t="inlineStr">
         <is>
-          <t>INN07CUX02 Tecweek Play</t>
+          <t>Derivación Becas Alimentarias - Fuera de horario de atención</t>
         </is>
       </c>
       <c r="B720" s="5" t="n">
@@ -9817,7 +9817,7 @@
     <row r="721">
       <c r="A721" t="inlineStr">
         <is>
-          <t>EM04CUX01 Grabados</t>
+          <t>MO05CUX03 Exitoso - charla virtual</t>
         </is>
       </c>
       <c r="B721" s="5" t="n">
@@ -9830,7 +9830,7 @@
     <row r="722">
       <c r="A722" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>GE03CUX02 Apertura</t>
         </is>
       </c>
       <c r="B722" s="5" t="n">
@@ -9843,7 +9843,7 @@
     <row r="723">
       <c r="A723" t="inlineStr">
         <is>
-          <t>EDU04CUX30 Celu en el aula</t>
+          <t>EM04CUX01 Grabados</t>
         </is>
       </c>
       <c r="B723" s="5" t="n">
@@ -9856,7 +9856,7 @@
     <row r="724">
       <c r="A724" t="inlineStr">
         <is>
-          <t>MO02CUX01 Lista de opciones</t>
+          <t>INN07CUX02 Tecweek Play</t>
         </is>
       </c>
       <c r="B724" s="5" t="n">
@@ -9869,7 +9869,7 @@
     <row r="725">
       <c r="A725" t="inlineStr">
         <is>
-          <t>TR03CUX03 Apertura</t>
+          <t>TR03CUX07 Apertura Inscripción al registro público de salvavidas</t>
         </is>
       </c>
       <c r="B725" s="5" t="n">
@@ -9882,7 +9882,7 @@
     <row r="726">
       <c r="A726" t="inlineStr">
         <is>
-          <t>Levantamiento de clausura ascensor</t>
+          <t>CO04CUX08 Apertura</t>
         </is>
       </c>
       <c r="B726" s="5" t="n">
@@ -9895,33 +9895,33 @@
     <row r="727">
       <c r="A727" t="inlineStr">
         <is>
-          <t>CU08CUX06 Verano en las plazas</t>
+          <t>Che</t>
         </is>
       </c>
       <c r="B727" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C727" s="6" t="n">
-        <v>1.915382243257376e-06</v>
+        <v>1.436536682443032e-06</v>
       </c>
     </row>
     <row r="728">
       <c r="A728" t="inlineStr">
         <is>
-          <t>DH08CUX03  Apertura de contingencia II</t>
+          <t>SUA01CUX27 No encontró ubicación</t>
         </is>
       </c>
       <c r="B728" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C728" s="6" t="n">
-        <v>1.915382243257376e-06</v>
+        <v>1.436536682443032e-06</v>
       </c>
     </row>
     <row r="729">
       <c r="A729" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Seleccionar hora - Por Lugar</t>
+          <t>TR01CUX01 Requisitos</t>
         </is>
       </c>
       <c r="B729" s="5" t="n">
@@ -9934,7 +9934,7 @@
     <row r="730">
       <c r="A730" t="inlineStr">
         <is>
-          <t>CU01CUX10 Apertura</t>
+          <t>Rendir subsidio 690</t>
         </is>
       </c>
       <c r="B730" s="5" t="n">
@@ -9947,7 +9947,7 @@
     <row r="731">
       <c r="A731" t="inlineStr">
         <is>
-          <t>CU01CUX10 BA Punto de partida</t>
+          <t>DDHH03CUX01 Chicos perdidos</t>
         </is>
       </c>
       <c r="B731" s="5" t="n">
@@ -9960,7 +9960,7 @@
     <row r="732">
       <c r="A732" t="inlineStr">
         <is>
-          <t>NI01CUX09 Sí, dale (Primer acto)</t>
+          <t>NI01CUX10 Inicio del cuento</t>
         </is>
       </c>
       <c r="B732" s="5" t="n">
@@ -9973,7 +9973,7 @@
     <row r="733">
       <c r="A733" t="inlineStr">
         <is>
-          <t>DH11CUX05 Encuesta</t>
+          <t xml:space="preserve">DH07CUX01 Cómo anotarme </t>
         </is>
       </c>
       <c r="B733" s="5" t="n">
@@ -9986,7 +9986,7 @@
     <row r="734">
       <c r="A734" t="inlineStr">
         <is>
-          <t>VI01CUX02 Destinatarios</t>
+          <t>MO10CUX04 Apertura</t>
         </is>
       </c>
       <c r="B734" s="5" t="n">
@@ -9999,7 +9999,7 @@
     <row r="735">
       <c r="A735" t="inlineStr">
         <is>
-          <t>¿Fumás?</t>
+          <t>TR02CUX04 Qué necesito</t>
         </is>
       </c>
       <c r="B735" s="5" t="n">
@@ -10012,7 +10012,7 @@
     <row r="736">
       <c r="A736" t="inlineStr">
         <is>
-          <t>mo05cux12 Esa opción ya la elegiste</t>
+          <t>TUR01CUX03 Elegir fecha</t>
         </is>
       </c>
       <c r="B736" s="5" t="n">
@@ -10025,7 +10025,7 @@
     <row r="737">
       <c r="A737" t="inlineStr">
         <is>
-          <t>Resultado hisopado negativo</t>
+          <t>AM04CUX06 Quiero ir</t>
         </is>
       </c>
       <c r="B737" s="5" t="n">
@@ -10038,7 +10038,7 @@
     <row r="738">
       <c r="A738" t="inlineStr">
         <is>
-          <t>DH03CUX03 Acompañantes</t>
+          <t>Dirección ya denunciada | Baches</t>
         </is>
       </c>
       <c r="B738" s="5" t="n">
@@ -10051,7 +10051,7 @@
     <row r="739">
       <c r="A739" t="inlineStr">
         <is>
-          <t>AM04CUX04 Visitas guiadas</t>
+          <t>Bicicletas (Apertura) &gt; Bicicleterías * Response</t>
         </is>
       </c>
       <c r="B739" s="5" t="n">
@@ -10064,7 +10064,7 @@
     <row r="740">
       <c r="A740" t="inlineStr">
         <is>
-          <t>Rendir subsidio 690</t>
+          <t>EDU04CUX19 Apertura</t>
         </is>
       </c>
       <c r="B740" s="5" t="n">
@@ -10077,7 +10077,7 @@
     <row r="741">
       <c r="A741" t="inlineStr">
         <is>
-          <t>AGC01CUX02 Libro Digital</t>
+          <t>AM04CUX03 Quiero ir</t>
         </is>
       </c>
       <c r="B741" s="5" t="n">
@@ -10090,7 +10090,7 @@
     <row r="742">
       <c r="A742" t="inlineStr">
         <is>
-          <t>TR04CUX16 Cómo lo tramito</t>
+          <t>AM04CUX04 Visitas guiadas</t>
         </is>
       </c>
       <c r="B742" s="5" t="n">
@@ -10103,7 +10103,7 @@
     <row r="743">
       <c r="A743" t="inlineStr">
         <is>
-          <t>AM04CUX06 Quiero ir</t>
+          <t>VI01CUX02 Cómo anotarse</t>
         </is>
       </c>
       <c r="B743" s="5" t="n">
@@ -10116,7 +10116,7 @@
     <row r="744">
       <c r="A744" t="inlineStr">
         <is>
-          <t>MO05CUX03 Validar datos</t>
+          <t>EM04CUX01 En vivo</t>
         </is>
       </c>
       <c r="B744" s="5" t="n">
@@ -10129,7 +10129,7 @@
     <row r="745">
       <c r="A745" t="inlineStr">
         <is>
-          <t>TR03CUX08 Obras</t>
+          <t>EM03CUX02 Cursos virtuales</t>
         </is>
       </c>
       <c r="B745" s="5" t="n">
@@ -10142,7 +10142,7 @@
     <row r="746">
       <c r="A746" t="inlineStr">
         <is>
-          <t>CU10CUX02 Isidoro Cañones</t>
+          <t>EP04CUX01 Chat por WhatsApp</t>
         </is>
       </c>
       <c r="B746" s="5" t="n">
@@ -10155,7 +10155,7 @@
     <row r="747">
       <c r="A747" t="inlineStr">
         <is>
-          <t>CU10CUX02 Diógenes y el Linyera</t>
+          <t>MO05CUX03 Validar datos</t>
         </is>
       </c>
       <c r="B747" s="5" t="n">
@@ -10168,7 +10168,7 @@
     <row r="748">
       <c r="A748" t="inlineStr">
         <is>
-          <t>Che</t>
+          <t>TR03CUX07 Apertura</t>
         </is>
       </c>
       <c r="B748" s="5" t="n">
@@ -10181,7 +10181,7 @@
     <row r="749">
       <c r="A749" t="inlineStr">
         <is>
-          <t>Filtro de segurización</t>
+          <t>CU01CUX07 Ciudades imaginadas</t>
         </is>
       </c>
       <c r="B749" s="5" t="n">
@@ -10194,7 +10194,7 @@
     <row r="750">
       <c r="A750" t="inlineStr">
         <is>
-          <t>TR01CUX09 Qué necesito</t>
+          <t>DH11CUX05 Encuesta</t>
         </is>
       </c>
       <c r="B750" s="5" t="n">
@@ -10207,7 +10207,7 @@
     <row r="751">
       <c r="A751" t="inlineStr">
         <is>
-          <t>EM04CUX01 En vivo</t>
+          <t>Derivación Becas Alimentarias - ✅ Auxiliar disponible</t>
         </is>
       </c>
       <c r="B751" s="5" t="n">
@@ -10220,7 +10220,7 @@
     <row r="752">
       <c r="A752" t="inlineStr">
         <is>
-          <t>TR01CUX09 Cómo hago el trámite</t>
+          <t>DH11CUX04 Chat por Whatsapp</t>
         </is>
       </c>
       <c r="B752" s="5" t="n">
@@ -10233,7 +10233,7 @@
     <row r="753">
       <c r="A753" t="inlineStr">
         <is>
-          <t>JU03CUX01 Tengo una consulta</t>
+          <t>CIU05CUX08 Sitios Históricos Caballito</t>
         </is>
       </c>
       <c r="B753" s="5" t="n">
@@ -10246,7 +10246,7 @@
     <row r="754">
       <c r="A754" t="inlineStr">
         <is>
-          <t>SE06CUX01 Más info útil</t>
+          <t>NI01CUX09 Escenario</t>
         </is>
       </c>
       <c r="B754" s="5" t="n">
@@ -10259,7 +10259,7 @@
     <row r="755">
       <c r="A755" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRO4CUX32  Subintent errores </t>
+          <t>NI01CUX01 Superapertura Boticlásicos</t>
         </is>
       </c>
       <c r="B755" s="5" t="n">
@@ -10272,7 +10272,7 @@
     <row r="756">
       <c r="A756" t="inlineStr">
         <is>
-          <t>EDU04CUX19 Apertura</t>
+          <t>Qué necesito | Certificado de Pobreza</t>
         </is>
       </c>
       <c r="B756" s="5" t="n">
@@ -10285,7 +10285,7 @@
     <row r="757">
       <c r="A757" t="inlineStr">
         <is>
-          <t>SUA01CUX27 No encontró ubicación</t>
+          <t>DEC05CUX02 Cómo participo</t>
         </is>
       </c>
       <c r="B757" s="5" t="n">
@@ -10298,7 +10298,7 @@
     <row r="758">
       <c r="A758" t="inlineStr">
         <is>
-          <t>MO10CUX01 Info para viajar</t>
+          <t>Resultado hisopado negativo</t>
         </is>
       </c>
       <c r="B758" s="5" t="n">
@@ -10311,7 +10311,7 @@
     <row r="759">
       <c r="A759" t="inlineStr">
         <is>
-          <t>NI01CUX10 Inicio del cuento</t>
+          <t>SA08CUX01 Requisitos</t>
         </is>
       </c>
       <c r="B759" s="5" t="n">
@@ -10324,7 +10324,7 @@
     <row r="760">
       <c r="A760" t="inlineStr">
         <is>
-          <t>EDU01CUX02 Qué carreras aplican</t>
+          <t>Cuánto cuesta | Fotocopia de Documentación Archivada</t>
         </is>
       </c>
       <c r="B760" s="5" t="n">
@@ -10337,7 +10337,7 @@
     <row r="761">
       <c r="A761" t="inlineStr">
         <is>
-          <t>DDHH03CUX01 Chicos perdidos</t>
+          <t>CU10CUX02 Diógenes y el Linyera</t>
         </is>
       </c>
       <c r="B761" s="5" t="n">
@@ -10350,7 +10350,7 @@
     <row r="762">
       <c r="A762" t="inlineStr">
         <is>
-          <t>MO10CUX04 Líneas</t>
+          <t>mo05cux12 Esa opción ya la elegiste</t>
         </is>
       </c>
       <c r="B762" s="5" t="n">
@@ -10363,7 +10363,7 @@
     <row r="763">
       <c r="A763" t="inlineStr">
         <is>
-          <t>Cuánto cuesta | Fotocopia de Documentación Archivada</t>
+          <t>¿Fumás?</t>
         </is>
       </c>
       <c r="B763" s="5" t="n">
@@ -10376,7 +10376,7 @@
     <row r="764">
       <c r="A764" t="inlineStr">
         <is>
-          <t>NI01CUX01 Superapertura Boticlásicos</t>
+          <t>TU03CUX01 Boca Juniors</t>
         </is>
       </c>
       <c r="B764" s="5" t="n">
@@ -10389,7 +10389,7 @@
     <row r="765">
       <c r="A765" t="inlineStr">
         <is>
-          <t>ED03CUX05 Licenciaturas</t>
+          <t>DH11CUX08 Pedido de datos</t>
         </is>
       </c>
       <c r="B765" s="5" t="n">
@@ -10402,7 +10402,7 @@
     <row r="766">
       <c r="A766" t="inlineStr">
         <is>
-          <t>Dirección ya denunciada | Baches</t>
+          <t xml:space="preserve">TRO4CUX32  Subintent errores </t>
         </is>
       </c>
       <c r="B766" s="5" t="n">
@@ -10415,85 +10415,85 @@
     <row r="767">
       <c r="A767" t="inlineStr">
         <is>
-          <t>SA08CUX01 Requisitos</t>
+          <t>TR03CUX08 Obras</t>
         </is>
       </c>
       <c r="B767" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C767" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>1.436536682443032e-06</v>
       </c>
     </row>
     <row r="768">
       <c r="A768" t="inlineStr">
         <is>
-          <t>fulfilled of Condición 2</t>
+          <t>Filtro de segurización</t>
         </is>
       </c>
       <c r="B768" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C768" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>1.436536682443032e-06</v>
       </c>
     </row>
     <row r="769">
       <c r="A769" t="inlineStr">
         <is>
-          <t>VI01CUX01 Pagar tu crédito</t>
+          <t>​​DH02CUX01 FONDES​</t>
         </is>
       </c>
       <c r="B769" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C769" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>1.436536682443032e-06</v>
       </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
         <is>
-          <t>CIU05CUX10 Murales La Boca</t>
+          <t>​​DH02CUX01 Apertura corta​</t>
         </is>
       </c>
       <c r="B770" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C770" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>1.436536682443032e-06</v>
       </c>
     </row>
     <row r="771">
       <c r="A771" t="inlineStr">
         <is>
-          <t>SE01CUX01 Quiero inscribirme</t>
+          <t>Derivación desde la web</t>
         </is>
       </c>
       <c r="B771" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C771" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>1.436536682443032e-06</v>
       </c>
     </row>
     <row r="772">
       <c r="A772" t="inlineStr">
         <is>
-          <t>SE02CUX01 Dónde denunciar</t>
+          <t>​​DH02CUX01 Beneficios impositivos​</t>
         </is>
       </c>
       <c r="B772" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C772" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>1.436536682443032e-06</v>
       </c>
     </row>
     <row r="773">
       <c r="A773" t="inlineStr">
         <is>
-          <t>SE02CUX02 Acoso digital</t>
+          <t>CIU05CUX08 Almagro</t>
         </is>
       </c>
       <c r="B773" s="5" t="n">
@@ -10506,7 +10506,7 @@
     <row r="774">
       <c r="A774" t="inlineStr">
         <is>
-          <t xml:space="preserve">SE01CUX01 Proceso de Selección </t>
+          <t>DH11CUX05 V1</t>
         </is>
       </c>
       <c r="B774" s="5" t="n">
@@ -10519,7 +10519,7 @@
     <row r="775">
       <c r="A775" t="inlineStr">
         <is>
-          <t>DH11CUX05 V3</t>
+          <t>TR03CUX25 Cómo pagar boletas</t>
         </is>
       </c>
       <c r="B775" s="5" t="n">
@@ -10532,7 +10532,7 @@
     <row r="776">
       <c r="A776" t="inlineStr">
         <is>
-          <t>DH11CUX07 Validación de datos</t>
+          <t>Empezar denuncia</t>
         </is>
       </c>
       <c r="B776" s="5" t="n">
@@ -10545,7 +10545,7 @@
     <row r="777">
       <c r="A777" t="inlineStr">
         <is>
-          <t xml:space="preserve">SE01CUX01 Cómo se cursa  </t>
+          <t>Easter egg River</t>
         </is>
       </c>
       <c r="B777" s="5" t="n">
@@ -10558,7 +10558,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>DH11CUX05  Apertura estático principal</t>
+          <t>EP05CUX01 Actividades</t>
         </is>
       </c>
       <c r="B778" s="5" t="n">
@@ -10571,7 +10571,7 @@
     <row r="779">
       <c r="A779" t="inlineStr">
         <is>
-          <t>NI01CUX11 Apertura inicio</t>
+          <t>Eliminar</t>
         </is>
       </c>
       <c r="B779" s="5" t="n">
@@ -10584,7 +10584,7 @@
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Por lugar &gt; No sirve</t>
+          <t>EDU05CUX02 * Estudio en BA</t>
         </is>
       </c>
       <c r="B780" s="5" t="n">
@@ -10597,7 +10597,7 @@
     <row r="781">
       <c r="A781" t="inlineStr">
         <is>
-          <t>AM03CUX04 Cuidados del agua</t>
+          <t>JU03CUX01 Cómo funciona</t>
         </is>
       </c>
       <c r="B781" s="5" t="n">
@@ -10610,7 +10610,7 @@
     <row r="782">
       <c r="A782" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Validar datos</t>
+          <t>GE03CUX02 Quiero capacitarme</t>
         </is>
       </c>
       <c r="B782" s="5" t="n">
@@ -10623,7 +10623,7 @@
     <row r="783">
       <c r="A783" t="inlineStr">
         <is>
-          <t>OB05CUX01 Número de expediente erróneo</t>
+          <t>TUR01CUX03 Por lugar &gt; No sirve</t>
         </is>
       </c>
       <c r="B783" s="5" t="n">
@@ -10636,7 +10636,7 @@
     <row r="784">
       <c r="A784" t="inlineStr">
         <is>
-          <t>OB05CUX01 Subsanación - 4D</t>
+          <t>AM03CUX04 Cuidados del agua</t>
         </is>
       </c>
       <c r="B784" s="5" t="n">
@@ -10649,7 +10649,7 @@
     <row r="785">
       <c r="A785" t="inlineStr">
         <is>
-          <t>SA17CUX01 Apertura</t>
+          <t>EDU05CUX01 Banco Ciudad</t>
         </is>
       </c>
       <c r="B785" s="5" t="n">
@@ -10662,7 +10662,7 @@
     <row r="786">
       <c r="A786" t="inlineStr">
         <is>
-          <t>Problema al ejecutar acciones de código</t>
+          <t xml:space="preserve">EDU04CUX30 Primera infancia </t>
         </is>
       </c>
       <c r="B786" s="5" t="n">
@@ -10675,7 +10675,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>Qué necesito | Certificado de Pobreza</t>
+          <t>EDU04CUX25 Se me bloqueó</t>
         </is>
       </c>
       <c r="B787" s="5" t="n">
@@ -10688,7 +10688,7 @@
     <row r="788">
       <c r="A788" t="inlineStr">
         <is>
-          <t>DH11CUX04 Chat por Whatsapp</t>
+          <t>Inactividad del usuario: Turismo MSFT</t>
         </is>
       </c>
       <c r="B788" s="5" t="n">
@@ -10701,7 +10701,7 @@
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>TU03CUX01 Boca Juniors</t>
+          <t>BX02CUX01 Pregunta 2</t>
         </is>
       </c>
       <c r="B789" s="5" t="n">
@@ -10727,7 +10727,7 @@
     <row r="791">
       <c r="A791" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Sitios Históricos Caballito</t>
+          <t>TR03CUX27 Seguridad en establecimientos de salud privados</t>
         </is>
       </c>
       <c r="B791" s="5" t="n">
@@ -10740,7 +10740,7 @@
     <row r="792">
       <c r="A792" t="inlineStr">
         <is>
-          <t>TR03CUX27 Seguridad en establecimientos de salud privados</t>
+          <t>CIU05CUX10 Murales La Boca</t>
         </is>
       </c>
       <c r="B792" s="5" t="n">
@@ -10753,7 +10753,7 @@
     <row r="793">
       <c r="A793" t="inlineStr">
         <is>
-          <t>TU01CUX05  Necesito ayuda</t>
+          <t>DH11CUX07 Validación de datos</t>
         </is>
       </c>
       <c r="B793" s="5" t="n">
@@ -10766,7 +10766,7 @@
     <row r="794">
       <c r="A794" t="inlineStr">
         <is>
-          <t>MO10CUX04 Apertura</t>
+          <t>DH11CUX07 Repaso V1</t>
         </is>
       </c>
       <c r="B794" s="5" t="n">
@@ -10779,7 +10779,7 @@
     <row r="795">
       <c r="A795" t="inlineStr">
         <is>
-          <t>MO10CUX01 Recorridos</t>
+          <t>EDU05CUX02 * Qué puedo estudiar (Estudio en BA)</t>
         </is>
       </c>
       <c r="B795" s="5" t="n">
@@ -10792,7 +10792,7 @@
     <row r="796">
       <c r="A796" t="inlineStr">
         <is>
-          <t>Mostrar más Resultados | Ecobici</t>
+          <t>Problema al ejecutar acciones de código</t>
         </is>
       </c>
       <c r="B796" s="5" t="n">
@@ -10805,7 +10805,7 @@
     <row r="797">
       <c r="A797" t="inlineStr">
         <is>
-          <t>Mantenimiento servicios</t>
+          <t>MO10CUX01 Info para viajar</t>
         </is>
       </c>
       <c r="B797" s="5" t="n">
@@ -10818,7 +10818,7 @@
     <row r="798">
       <c r="A798" t="inlineStr">
         <is>
-          <t>DDHH01CUX01 Residencia y DNI</t>
+          <t>NI01CUX11 Apertura inicio</t>
         </is>
       </c>
       <c r="B798" s="5" t="n">
@@ -10831,7 +10831,7 @@
     <row r="799">
       <c r="A799" t="inlineStr">
         <is>
-          <t>MO10CUX06 Líneas</t>
+          <t>TR01CUX03 Requisitos</t>
         </is>
       </c>
       <c r="B799" s="5" t="n">
@@ -10844,7 +10844,7 @@
     <row r="800">
       <c r="A800" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Almagro</t>
+          <t>MO10CUX04 Líneas</t>
         </is>
       </c>
       <c r="B800" s="5" t="n">
@@ -10857,7 +10857,7 @@
     <row r="801">
       <c r="A801" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Barrio Inglés</t>
+          <t>DH05CUX01 Hablar con alguien</t>
         </is>
       </c>
       <c r="B801" s="5" t="n">
@@ -10870,7 +10870,7 @@
     <row r="802">
       <c r="A802" t="inlineStr">
         <is>
-          <t>EDU05CUX02 * Estudio en BA</t>
+          <t>DH05CUX01 Centros Barriales</t>
         </is>
       </c>
       <c r="B802" s="5" t="n">
@@ -10883,7 +10883,7 @@
     <row r="803">
       <c r="A803" t="inlineStr">
         <is>
-          <t>TR03CUX07 Apertura Inscripción al registro público de salvavidas</t>
+          <t>TR01CUX04 Cómo hago el trámite</t>
         </is>
       </c>
       <c r="B803" s="5" t="n">
@@ -10896,7 +10896,7 @@
     <row r="804">
       <c r="A804" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDU07CUX01 Secundario </t>
+          <t>DH06CUX01 Tipos de sellos</t>
         </is>
       </c>
       <c r="B804" s="5" t="n">
@@ -10909,7 +10909,7 @@
     <row r="805">
       <c r="A805" t="inlineStr">
         <is>
-          <t>CU04CUX57 Sueño stereo</t>
+          <t>CU04CUX57 Gala lírica</t>
         </is>
       </c>
       <c r="B805" s="5" t="n">
@@ -10922,7 +10922,7 @@
     <row r="806">
       <c r="A806" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cómo hacerlo | Disolución de Unión Civil / Convivencial </t>
+          <t>PC03CUX01 Voluntarios BA</t>
         </is>
       </c>
       <c r="B806" s="5" t="n">
@@ -10935,7 +10935,7 @@
     <row r="807">
       <c r="A807" t="inlineStr">
         <is>
-          <t>Cómo es el trámite</t>
+          <t>CU01CUX15 Las Cabras Macabras</t>
         </is>
       </c>
       <c r="B807" s="5" t="n">
@@ -10948,7 +10948,7 @@
     <row r="808">
       <c r="A808" t="inlineStr">
         <is>
-          <t>Código postal - No pudo encontrarlo por ubicación</t>
+          <t>DH11CUX03 Responder pregunta MTV1</t>
         </is>
       </c>
       <c r="B808" s="5" t="n">
@@ -10961,7 +10961,7 @@
     <row r="809">
       <c r="A809" t="inlineStr">
         <is>
-          <t>Easter egg River</t>
+          <t>Mantenimiento servicios</t>
         </is>
       </c>
       <c r="B809" s="5" t="n">
@@ -10974,7 +10974,7 @@
     <row r="810">
       <c r="A810" t="inlineStr">
         <is>
-          <t>EP04CUX01 Chat por WhatsApp</t>
+          <t>CU01CUX14 Info útil</t>
         </is>
       </c>
       <c r="B810" s="5" t="n">
@@ -10987,7 +10987,7 @@
     <row r="811">
       <c r="A811" t="inlineStr">
         <is>
-          <t>TR01CUX01 Requisitos</t>
+          <t>Mostrar más Resultados | Servicio de Cercanía</t>
         </is>
       </c>
       <c r="B811" s="5" t="n">
@@ -11000,7 +11000,7 @@
     <row r="812">
       <c r="A812" t="inlineStr">
         <is>
-          <t>Suaci - Error de foto obligatoria</t>
+          <t>CUL02CUX03 Iglesias y templos Devoto</t>
         </is>
       </c>
       <c r="B812" s="5" t="n">
@@ -11013,7 +11013,7 @@
     <row r="813">
       <c r="A813" t="inlineStr">
         <is>
-          <t>Inactividad del usuario: Turismo MSFT</t>
+          <t>fulfilled of ADICCIONES</t>
         </is>
       </c>
       <c r="B813" s="5" t="n">
@@ -11026,7 +11026,7 @@
     <row r="814">
       <c r="A814" t="inlineStr">
         <is>
-          <t>TR01CUX04 Cómo hago el trámite</t>
+          <t>CUL02CUX01 Apertura</t>
         </is>
       </c>
       <c r="B814" s="5" t="n">
@@ -11039,7 +11039,7 @@
     <row r="815">
       <c r="A815" t="inlineStr">
         <is>
-          <t>Hablar con operador</t>
+          <t>SA17CUX01 Apertura</t>
         </is>
       </c>
       <c r="B815" s="5" t="n">
@@ -11052,7 +11052,7 @@
     <row r="816">
       <c r="A816" t="inlineStr">
         <is>
-          <t>TR01CUX15 Hacer el registro</t>
+          <t>DH05CUX01 Apertura corta</t>
         </is>
       </c>
       <c r="B816" s="5" t="n">
@@ -11065,7 +11065,7 @@
     <row r="817">
       <c r="A817" t="inlineStr">
         <is>
-          <t>TR01CUX15 Requisitos</t>
+          <t>CU09CUX03 Visitas guiadas</t>
         </is>
       </c>
       <c r="B817" s="5" t="n">
@@ -11078,7 +11078,7 @@
     <row r="818">
       <c r="A818" t="inlineStr">
         <is>
-          <t>CUL02CUX03 Iglesias y templos Devoto</t>
+          <t>DDHH03CUX05 Hacer una consulta</t>
         </is>
       </c>
       <c r="B818" s="5" t="n">
@@ -11091,7 +11091,7 @@
     <row r="819">
       <c r="A819" t="inlineStr">
         <is>
-          <t>CUL02CUX01 Apertura</t>
+          <t>DE00CUX03 Polideportivos</t>
         </is>
       </c>
       <c r="B819" s="5" t="n">
@@ -11104,7 +11104,7 @@
     <row r="820">
       <c r="A820" t="inlineStr">
         <is>
-          <t>BX02CUX01 Pregunta 3</t>
+          <t>DDHH01CUX01 Qué necesito</t>
         </is>
       </c>
       <c r="B820" s="5" t="n">
@@ -11117,7 +11117,7 @@
     <row r="821">
       <c r="A821" t="inlineStr">
         <is>
-          <t>TR02CUX04 Qué necesito</t>
+          <t xml:space="preserve">EDU07CUX01 Secundario </t>
         </is>
       </c>
       <c r="B821" s="5" t="n">
@@ -11130,7 +11130,7 @@
     <row r="822">
       <c r="A822" t="inlineStr">
         <is>
-          <t>Empezar denuncia</t>
+          <t>fulfilled of Condición 2</t>
         </is>
       </c>
       <c r="B822" s="5" t="n">
@@ -11143,150 +11143,150 @@
     <row r="823">
       <c r="A823" t="inlineStr">
         <is>
-          <t>Eliminar</t>
+          <t>CU09CUX03 Dónde queda</t>
         </is>
       </c>
       <c r="B823" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C823" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>4.788455608143439e-07</v>
       </c>
     </row>
     <row r="824">
       <c r="A824" t="inlineStr">
         <is>
-          <t>Bicicletas (Apertura) &gt; Bicicleterías * Response</t>
+          <t>CU04CUX41 Apertura corta variante 2</t>
         </is>
       </c>
       <c r="B824" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C824" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>4.788455608143439e-07</v>
       </c>
     </row>
     <row r="825">
       <c r="A825" t="inlineStr">
         <is>
-          <t>​​DH02CUX01 FONDES​</t>
+          <t>DEC03CUX01 Espacios BA</t>
         </is>
       </c>
       <c r="B825" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C825" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>4.788455608143439e-07</v>
       </c>
     </row>
     <row r="826">
       <c r="A826" t="inlineStr">
         <is>
-          <t>fulfilled of ADICCIONES</t>
+          <t>DEC05CUX02 De qué se trata</t>
         </is>
       </c>
       <c r="B826" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C826" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>4.788455608143439e-07</v>
       </c>
     </row>
     <row r="827">
       <c r="A827" t="inlineStr">
         <is>
-          <t>​​DH02CUX01 Requisitos​</t>
+          <t>¿En qué consiste el trámite de Modificación de Datos?</t>
         </is>
       </c>
       <c r="B827" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C827" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>4.788455608143439e-07</v>
       </c>
     </row>
     <row r="828">
       <c r="A828" t="inlineStr">
         <is>
-          <t>​​DH02CUX01 Beneficios impositivos​</t>
+          <t>DH08CUX03  Apertura de contingencia III</t>
         </is>
       </c>
       <c r="B828" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C828" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>4.788455608143439e-07</v>
       </c>
     </row>
     <row r="829">
       <c r="A829" t="inlineStr">
         <is>
-          <t>AM04CUX04 Dónde queda</t>
+          <t>MO10CUX05 Líneas</t>
         </is>
       </c>
       <c r="B829" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C829" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>4.788455608143439e-07</v>
       </c>
     </row>
     <row r="830">
       <c r="A830" t="inlineStr">
         <is>
-          <t>DH02CUX01 Créditos emprendedores</t>
+          <t>NI01CUX07 Galera</t>
         </is>
       </c>
       <c r="B830" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C830" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>4.788455608143439e-07</v>
       </c>
     </row>
     <row r="831">
       <c r="A831" t="inlineStr">
         <is>
-          <t>DH04CUX05 Hacer consulta</t>
+          <t>NI01CUX06 Principio</t>
         </is>
       </c>
       <c r="B831" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C831" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>4.788455608143439e-07</v>
       </c>
     </row>
     <row r="832">
       <c r="A832" t="inlineStr">
         <is>
-          <t>DH05CUX01 Centros ambulatorios</t>
+          <t>NI01CUX09 Encuentro con el pato</t>
         </is>
       </c>
       <c r="B832" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C832" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>4.788455608143439e-07</v>
       </c>
     </row>
     <row r="833">
       <c r="A833" t="inlineStr">
         <is>
-          <t>DE00CUX03 Polideportivos</t>
+          <t xml:space="preserve">NI01CUX09 Asientos </t>
         </is>
       </c>
       <c r="B833" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C833" s="6" t="n">
-        <v>9.576911216286878e-07</v>
+        <v>4.788455608143439e-07</v>
       </c>
     </row>
     <row r="834">
       <c r="A834" t="inlineStr">
         <is>
-          <t>DEC03CUX01 Espacios BA</t>
+          <t>NI01CUX02  Apertura</t>
         </is>
       </c>
       <c r="B834" s="5" t="n">
@@ -11299,7 +11299,7 @@
     <row r="835">
       <c r="A835" t="inlineStr">
         <is>
-          <t>DH02CUX01 Quiero anotarme</t>
+          <t>NI01CUX02  Que charlen un rato</t>
         </is>
       </c>
       <c r="B835" s="5" t="n">
@@ -11312,7 +11312,7 @@
     <row r="836">
       <c r="A836" t="inlineStr">
         <is>
-          <t>TUR01CUX13 Ya tenía turno</t>
+          <t>CU01CUX11 Apertura</t>
         </is>
       </c>
       <c r="B836" s="5" t="n">
@@ -11325,7 +11325,7 @@
     <row r="837">
       <c r="A837" t="inlineStr">
         <is>
-          <t>a</t>
+          <t>CU01CUX10 BA en construcción</t>
         </is>
       </c>
       <c r="B837" s="5" t="n">
@@ -11338,7 +11338,7 @@
     <row r="838">
       <c r="A838" t="inlineStr">
         <is>
-          <t>Volver a consultar Código Postal</t>
+          <t>CU01CUX10 BA Punto de partida</t>
         </is>
       </c>
       <c r="B838" s="5" t="n">
@@ -11351,7 +11351,7 @@
     <row r="839">
       <c r="A839" t="inlineStr">
         <is>
-          <t>¿Tomás mate?</t>
+          <t>TR01CUX18 Pedí la constancia</t>
         </is>
       </c>
       <c r="B839" s="5" t="n">
@@ -11364,7 +11364,7 @@
     <row r="840">
       <c r="A840" t="inlineStr">
         <is>
-          <t>📅 Sacar un turno</t>
+          <t>CU01CUX07 Patio</t>
         </is>
       </c>
       <c r="B840" s="5" t="n">
@@ -11377,7 +11377,7 @@
     <row r="841">
       <c r="A841" t="inlineStr">
         <is>
-          <t>GA03CUX03 Apertura corta</t>
+          <t>CU01CUX15 Comienzo - Cabras Pista 1</t>
         </is>
       </c>
       <c r="B841" s="5" t="n">
@@ -11390,7 +11390,7 @@
     <row r="842">
       <c r="A842" t="inlineStr">
         <is>
-          <t>CUL02CUX03 Iglesias y templos Caballito</t>
+          <t>PiaW Falla en el servicio de audio</t>
         </is>
       </c>
       <c r="B842" s="5" t="n">
@@ -11403,7 +11403,7 @@
     <row r="843">
       <c r="A843" t="inlineStr">
         <is>
-          <t>CUL01CUX03 Eventos especiales</t>
+          <t>OB05CUX01 Número de expediente erróneo</t>
         </is>
       </c>
       <c r="B843" s="5" t="n">
@@ -11416,7 +11416,7 @@
     <row r="844">
       <c r="A844" t="inlineStr">
         <is>
-          <t>Banner BAX web</t>
+          <t>TR01CUX01 Cómo hago el trámite</t>
         </is>
       </c>
       <c r="B844" s="5" t="n">
@@ -11429,7 +11429,7 @@
     <row r="845">
       <c r="A845" t="inlineStr">
         <is>
-          <t>TR02CUX04 Cómo es el trámite</t>
+          <t>Qué necesito espectáculos musicales en vivo</t>
         </is>
       </c>
       <c r="B845" s="5" t="n">
@@ -11442,7 +11442,7 @@
     <row r="846">
       <c r="A846" t="inlineStr">
         <is>
-          <t>EDU05CUX05 Portugués</t>
+          <t>Prueba disparador para cola de atencion</t>
         </is>
       </c>
       <c r="B846" s="5" t="n">
@@ -11455,7 +11455,7 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>Código postal - Error del Servidor</t>
+          <t>DH07CUX01 Acompañamiento</t>
         </is>
       </c>
       <c r="B847" s="5" t="n">
@@ -11468,7 +11468,7 @@
     <row r="848">
       <c r="A848" t="inlineStr">
         <is>
-          <t>EM04CUX02 Tipos de crédito mujeres emprendedoras</t>
+          <t>OB05CUX01 Otro estado - 6A</t>
         </is>
       </c>
       <c r="B848" s="5" t="n">
@@ -11481,7 +11481,7 @@
     <row r="849">
       <c r="A849" t="inlineStr">
         <is>
-          <t>EM03CUX02 Cursos presenciales</t>
+          <t>OB05CUX01 Subsanación - 4D</t>
         </is>
       </c>
       <c r="B849" s="5" t="n">
@@ -11494,7 +11494,7 @@
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>Bicicletas (Apertura) &gt; Dónde dejar la bici * Ap de flow</t>
+          <t>Partidas extranjeras - Casados y divorciados en el exterior</t>
         </is>
       </c>
       <c r="B850" s="5" t="n">
@@ -11507,7 +11507,7 @@
     <row r="851">
       <c r="A851" t="inlineStr">
         <is>
-          <t>TR01CUX18 Pedí la constancia</t>
+          <t>TR01CUX08 Cómo hago el trámite</t>
         </is>
       </c>
       <c r="B851" s="5" t="n">
@@ -11520,7 +11520,7 @@
     <row r="852">
       <c r="A852" t="inlineStr">
         <is>
-          <t>TR01CUX11 Qué necesito</t>
+          <t>OB05CUX01 Guarda Temporal - 5A</t>
         </is>
       </c>
       <c r="B852" s="5" t="n">
@@ -11533,7 +11533,7 @@
     <row r="853">
       <c r="A853" t="inlineStr">
         <is>
-          <t>INN10CUX01 Cómo funciona</t>
+          <t>NI01CUX11 Un jarabe Conejos</t>
         </is>
       </c>
       <c r="B853" s="5" t="n">
@@ -11546,7 +11546,7 @@
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>Hablar con una persona</t>
+          <t>TR01CUX05 Qué necesito</t>
         </is>
       </c>
       <c r="B854" s="5" t="n">
@@ -11559,7 +11559,7 @@
     <row r="855">
       <c r="A855" t="inlineStr">
         <is>
-          <t>GE03CUX02 Quiero capacitarme</t>
+          <t>DH02CUX01 Quiero anotarme</t>
         </is>
       </c>
       <c r="B855" s="5" t="n">
@@ -11572,7 +11572,7 @@
     <row r="856">
       <c r="A856" t="inlineStr">
         <is>
-          <t>TR01CUX03 Requisitos</t>
+          <t xml:space="preserve">DH02CUX01 Oportunidades </t>
         </is>
       </c>
       <c r="B856" s="5" t="n">
@@ -11585,7 +11585,7 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>TR01CUX01 Cómo hago el trámite</t>
+          <t>DH06CUX01 Cómo anotarse</t>
         </is>
       </c>
       <c r="B857" s="5" t="n">
@@ -11598,7 +11598,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>CU09CUX03 Dónde queda</t>
+          <t>TR01CUX09 Cómo hago el trámite</t>
         </is>
       </c>
       <c r="B858" s="5" t="n">
@@ -11611,7 +11611,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>JU03CUX01 Qué necesito</t>
+          <t>TR01CUX11 Qué necesito</t>
         </is>
       </c>
       <c r="B859" s="5" t="n">
@@ -11624,7 +11624,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>JU03CUX01 Cómo funciona</t>
+          <t>SA17CUX01 Sí – Está en el padrón</t>
         </is>
       </c>
       <c r="B860" s="5" t="n">
@@ -11637,7 +11637,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>JU03CUX01 Conocer mis derechos</t>
+          <t>SAC05CUX01 En horario disponible</t>
         </is>
       </c>
       <c r="B861" s="5" t="n">
@@ -11650,7 +11650,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>JU02CUX01 Hacer una consulta</t>
+          <t>CUL01CUX03 Eventos especiales</t>
         </is>
       </c>
       <c r="B862" s="5" t="n">
@@ -11663,7 +11663,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>Infracción - Licencia o Vehículo Retenido</t>
+          <t>SA16CUX02 Dosis de refuerzo</t>
         </is>
       </c>
       <c r="B863" s="5" t="n">
@@ -11676,7 +11676,7 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>EDU05CUX02 * Study BA</t>
+          <t>Cómo me inscribo para Registrar un bar</t>
         </is>
       </c>
       <c r="B864" s="5" t="n">
@@ -11689,7 +11689,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>EDU05CUX02 * Qué puedo estudiar (Estudio en BA)</t>
+          <t>SE01CUX04 Recomendaciones</t>
         </is>
       </c>
       <c r="B865" s="5" t="n">
@@ -11702,7 +11702,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>EDU05CUX02 * Fechas claves (Estudio en BA)</t>
+          <t>SE02CUX02 Acoso digital</t>
         </is>
       </c>
       <c r="B866" s="5" t="n">
@@ -11715,7 +11715,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDU04CUX30 Primera infancia </t>
+          <t>SE02CUX02 Protección infantil</t>
         </is>
       </c>
       <c r="B867" s="5" t="n">
@@ -11728,7 +11728,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t xml:space="preserve">EDU04CUX30 Niñez </t>
+          <t>fulfilled of Otro Tramite</t>
         </is>
       </c>
       <c r="B868" s="5" t="n">
@@ -11741,7 +11741,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>SUA01CUX26 Pedido de número de expediente</t>
+          <t>Código postal - Error del Servidor</t>
         </is>
       </c>
       <c r="B869" s="5" t="n">
@@ -11754,7 +11754,7 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>CU10CUX02 Mafalda &gt; Mapa del recorrido</t>
+          <t>¿Tomás mate?</t>
         </is>
       </c>
       <c r="B870" s="5" t="n">
@@ -11767,7 +11767,7 @@
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>CU04CUX57 Gala lírica</t>
+          <t>EDU05CUX02 * Study BA</t>
         </is>
       </c>
       <c r="B871" s="5" t="n">
@@ -11780,7 +11780,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Sitios Históricos Pasaje Gardel</t>
+          <t>VI01CUX06 Monto del préstamo</t>
         </is>
       </c>
       <c r="B872" s="5" t="n">
@@ -11793,7 +11793,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Sitios Históricos La Boca</t>
+          <t>EDU05CUX05 Portugués</t>
         </is>
       </c>
       <c r="B873" s="5" t="n">
@@ -11806,7 +11806,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Sitios Históricos Devoto</t>
+          <t>a</t>
         </is>
       </c>
       <c r="B874" s="5" t="n">
@@ -11819,7 +11819,7 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>TR03CUX27 Programa Prevención Mayor</t>
+          <t>Volver a consultar Código Postal</t>
         </is>
       </c>
       <c r="B875" s="5" t="n">
@@ -11832,7 +11832,7 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>TR03CUX27 Mediación comunitaria</t>
+          <t>DEC01CUX01 Cursos y talleres</t>
         </is>
       </c>
       <c r="B876" s="5" t="n">
@@ -11845,7 +11845,7 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>DDHH03CUX05 Hacer una consulta</t>
+          <t>DE05CUX04 Contacto</t>
         </is>
       </c>
       <c r="B877" s="5" t="n">
@@ -11858,7 +11858,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>DDHH03CUX04 Qué servicios hay</t>
+          <t>DDHH03CUX09 Qué necesito</t>
         </is>
       </c>
       <c r="B878" s="5" t="n">
@@ -11871,7 +11871,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>DDHH03CUX02 Quiero adoptar</t>
+          <t>SA08CUX01 Buscar hospitales</t>
         </is>
       </c>
       <c r="B879" s="5" t="n">
@@ -11884,7 +11884,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>EDU04CUX29 Horarios</t>
+          <t>DDHH03CUX09 De qué se trata</t>
         </is>
       </c>
       <c r="B880" s="5" t="n">
@@ -11897,7 +11897,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>TR03CUX25 Estado de mi trámite</t>
+          <t>CUL02CUX03 Iglesias y templos Caballito</t>
         </is>
       </c>
       <c r="B881" s="5" t="n">
@@ -11910,7 +11910,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>TR03CUX25 Cómo pagar boletas</t>
+          <t>SUA01CUX01 Direccion</t>
         </is>
       </c>
       <c r="B882" s="5" t="n">
@@ -11923,7 +11923,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Puente transbordador</t>
+          <t>Resolver Ubicación Domicilio | Fachada</t>
         </is>
       </c>
       <c r="B883" s="5" t="n">
@@ -11936,7 +11936,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Parque Onega</t>
+          <t>CU04CUX57 Sueño stereo</t>
         </is>
       </c>
       <c r="B884" s="5" t="n">
@@ -11949,7 +11949,7 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Otros sitios Caballito</t>
+          <t>SUA01CUX15 No Encontró Ubicación | Desagote de pozo</t>
         </is>
       </c>
       <c r="B885" s="5" t="n">
@@ -11962,7 +11962,7 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>CIU05CUX08 El Castillito</t>
+          <t>CU11CUX02 Cómo me inscribo</t>
         </is>
       </c>
       <c r="B886" s="5" t="n">
@@ -11975,7 +11975,7 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Colegiales</t>
+          <t>SA01CUX01N Tips de prevención</t>
         </is>
       </c>
       <c r="B887" s="5" t="n">
@@ -11988,7 +11988,7 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>CIU05CUX08 Calle de las flores</t>
+          <t>MO06CUX03 Necesito ayuda</t>
         </is>
       </c>
       <c r="B888" s="5" t="n">
@@ -12001,7 +12001,7 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>SUA01CUX01 Direccion</t>
+          <t>DH11CUX05 V4</t>
         </is>
       </c>
       <c r="B889" s="5" t="n">
@@ -12014,7 +12014,7 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>MO06CUX03 Necesito ayuda</t>
+          <t>DH11CUX05 Validación de datos</t>
         </is>
       </c>
       <c r="B890" s="5" t="n">
@@ -12027,7 +12027,7 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>MO10CUX07 Combinaciones</t>
+          <t>DH11CUX06 desde webchat</t>
         </is>
       </c>
       <c r="B891" s="5" t="n">
@@ -12040,7 +12040,7 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>DH11CUX08 Repaso video 3</t>
+          <t>TU03CUX02 Apertura</t>
         </is>
       </c>
       <c r="B892" s="5" t="n">
@@ -12053,7 +12053,7 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>TR05CUX04 CUIT CUIL inválido</t>
+          <t>TU03CUX01 Otros estadios</t>
         </is>
       </c>
       <c r="B893" s="5" t="n">
@@ -12066,7 +12066,7 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>Acciones previas a cada mensaje</t>
+          <t>Derivacion especialista</t>
         </is>
       </c>
       <c r="B894" s="5" t="n">
@@ -12079,7 +12079,7 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>DDHH01CUX01 Documentos</t>
+          <t>DH11CUX08 Video 3 Pregunta 2</t>
         </is>
       </c>
       <c r="B895" s="5" t="n">
@@ -12092,7 +12092,7 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>Cómo me inscribo para Registrar un bar</t>
+          <t>DH11CUX08 Video 1 Pregunta 1</t>
         </is>
       </c>
       <c r="B896" s="5" t="n">
@@ -12105,7 +12105,7 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>Dónde lo hago | Información sumaria testimonial</t>
+          <t>DH11CUX08 Video 2 Pregunta 1</t>
         </is>
       </c>
       <c r="B897" s="5" t="n">
@@ -12118,7 +12118,7 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>MO10CUX05 Líneas</t>
+          <t>DH11CUX08 Validación de datos</t>
         </is>
       </c>
       <c r="B898" s="5" t="n">
@@ -12131,7 +12131,7 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>MO10CUX01 Otros recorridos</t>
+          <t>DH11CUX08 Repaso video 3</t>
         </is>
       </c>
       <c r="B899" s="5" t="n">
@@ -12144,7 +12144,7 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>MO10CUX01 Apertura corta</t>
+          <t>TU01CUX15 Cotización</t>
         </is>
       </c>
       <c r="B900" s="5" t="n">
@@ -12157,7 +12157,7 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>NI01CUX06 Principio</t>
+          <t>TU02CUX01 Esquina Maradona</t>
         </is>
       </c>
       <c r="B901" s="5" t="n">
@@ -12170,7 +12170,7 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>NI01CUX02  Que charlen un rato</t>
+          <t>CIU05CUX08 San Diego La Boca</t>
         </is>
       </c>
       <c r="B902" s="5" t="n">
@@ -12183,7 +12183,7 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>NI01CUX02  Inventar algo</t>
+          <t>DH11CUX05  Apertura de contingencia I</t>
         </is>
       </c>
       <c r="B903" s="5" t="n">
@@ -12196,7 +12196,7 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>Mostrar más Resultados | Servicio de Cercanía</t>
+          <t>CIU05CUX08 Seminario metropolitano</t>
         </is>
       </c>
       <c r="B904" s="5" t="n">
@@ -12209,7 +12209,7 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>TU03CUX02 Apertura</t>
+          <t>DH11CUX05 Repaso V4</t>
         </is>
       </c>
       <c r="B905" s="5" t="n">
@@ -12222,7 +12222,7 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>TU02CUX01 Esquina Maradona</t>
+          <t>DH11CUX05 Repaso V1</t>
         </is>
       </c>
       <c r="B906" s="5" t="n">
@@ -12235,7 +12235,7 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>TU01CUX15 Cotización</t>
+          <t>CIU05CUX08 Sitios Históricos Balvanera</t>
         </is>
       </c>
       <c r="B907" s="5" t="n">
@@ -12248,7 +12248,7 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>Dormís</t>
+          <t>DH11CUX05  Apertura estático principal</t>
         </is>
       </c>
       <c r="B908" s="5" t="n">
@@ -12261,7 +12261,7 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>Disambiguation Intent</t>
+          <t>DH11CUX07 Introducción</t>
         </is>
       </c>
       <c r="B909" s="5" t="n">
@@ -12274,7 +12274,7 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>Derivacion especialista</t>
+          <t>DH11CUX07 Apertura QR</t>
         </is>
       </c>
       <c r="B910" s="5" t="n">
@@ -12287,7 +12287,7 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>DH11CUX08 Video 3 Pregunta 2</t>
+          <t>DH11CUX07 Apertura</t>
         </is>
       </c>
       <c r="B911" s="5" t="n">
@@ -12300,7 +12300,7 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>DH11CUX08 Validación de datos</t>
+          <t>CIU05CUX10 Otros murales Colegiales</t>
         </is>
       </c>
       <c r="B912" s="5" t="n">
@@ -12313,7 +12313,7 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>MO10CUX07 Por dónde pasa</t>
+          <t>CIU05CUX10 Red Sudakas</t>
         </is>
       </c>
       <c r="B913" s="5" t="n">
@@ -12326,7 +12326,7 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>CO02CUX02 Cómo denunciar</t>
+          <t>CU01CUX07 Contracultura</t>
         </is>
       </c>
       <c r="B914" s="5" t="n">
@@ -12339,7 +12339,7 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>CIU05CUX12 Envío exitoso</t>
+          <t>MO09CUX04 Nuevo parque</t>
         </is>
       </c>
       <c r="B915" s="5" t="n">
@@ -12352,7 +12352,7 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>CIU05CUX10 Otros murales Colegiales</t>
+          <t>CO08CUX07 Cómo llego</t>
         </is>
       </c>
       <c r="B916" s="5" t="n">
@@ -12365,7 +12365,7 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>CIU05CUX10 Murales Caballito</t>
+          <t>CO02CUX02 Cómo denunciar</t>
         </is>
       </c>
       <c r="B917" s="5" t="n">
@@ -12378,7 +12378,7 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>CO08CUX07 Tren</t>
+          <t>TR03CUX27 Mediación comunitaria</t>
         </is>
       </c>
       <c r="B918" s="5" t="n">
@@ -12391,7 +12391,7 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>NI01CUX09 Pista de skate</t>
+          <t>CO08CUX07 Sobre las pistas</t>
         </is>
       </c>
       <c r="B919" s="5" t="n">
@@ -12404,7 +12404,7 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Elegir fecha</t>
+          <t>TR03CUX27 Retiro del vehículo acarreado abandonado</t>
         </is>
       </c>
       <c r="B920" s="5" t="n">
@@ -12417,7 +12417,7 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>TU03CUX13 Apertura</t>
+          <t>CIU05CUX08 Barrio Inglés</t>
         </is>
       </c>
       <c r="B921" s="5" t="n">
@@ -12430,7 +12430,7 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>DH11CUX07 Video 2</t>
+          <t>CIU05CUX08 Calle de las flores</t>
         </is>
       </c>
       <c r="B922" s="5" t="n">
@@ -12443,7 +12443,7 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>DH11CUX07 Video 1</t>
+          <t>CIU05CUX08 Estatua de la Libertad</t>
         </is>
       </c>
       <c r="B923" s="5" t="n">
@@ -12456,7 +12456,7 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>DH11CUX07 Silencio user</t>
+          <t>DH11CUX03  Apertura estático principal</t>
         </is>
       </c>
       <c r="B924" s="5" t="n">
@@ -12469,7 +12469,7 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>DH11CUX07 Corregir datos II</t>
+          <t>TR03CUX08 Presentación de informes bromatológicos</t>
         </is>
       </c>
       <c r="B925" s="5" t="n">
@@ -12482,7 +12482,7 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>DH11CUX07 Apertura</t>
+          <t>TR03CUX08 Más de Habilitaciones</t>
         </is>
       </c>
       <c r="B926" s="5" t="n">
@@ -12495,7 +12495,7 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>DH11CUX06 desde webchat</t>
+          <t>CO12CUX02 Número de emergencia</t>
         </is>
       </c>
       <c r="B927" s="5" t="n">
@@ -12508,7 +12508,7 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>DH11CUX05 Responder pregunta V3</t>
+          <t>Hablar con una persona</t>
         </is>
       </c>
       <c r="B928" s="5" t="n">
@@ -12521,7 +12521,7 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>DH11CUX05 Responde bien V3</t>
+          <t>Dormís</t>
         </is>
       </c>
       <c r="B929" s="5" t="n">
@@ -12534,7 +12534,7 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>DH11CUX05 Repaso V1</t>
+          <t>TUR01CUX03 Elegir tipo de turrno</t>
         </is>
       </c>
       <c r="B930" s="5" t="n">
@@ -12547,7 +12547,7 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>DH11CUX05  Apertura de contingencia I</t>
+          <t>TUR01CUX03 Por fecha</t>
         </is>
       </c>
       <c r="B931" s="5" t="n">
@@ -12560,7 +12560,7 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>NI01CUX07 Galera</t>
+          <t>Disambiguation Intent</t>
         </is>
       </c>
       <c r="B932" s="5" t="n">
@@ -12573,7 +12573,7 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>CU04CUX41 Bares recomendados</t>
+          <t>Infracción - Licencia o Vehículo Retenido</t>
         </is>
       </c>
       <c r="B933" s="5" t="n">
@@ -12586,7 +12586,7 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>Partidas extranjeras - Casados y divorciados en el exterior</t>
+          <t>Dónde lo hago | Información sumaria testimonial</t>
         </is>
       </c>
       <c r="B934" s="5" t="n">
@@ -12599,7 +12599,7 @@
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>OB05CUX01 Subsanación - 4A</t>
+          <t>Banner BAX web</t>
         </is>
       </c>
       <c r="B935" s="5" t="n">
@@ -12612,7 +12612,7 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>NI01CUX11 Tunel en grupo plot point II</t>
+          <t>BX02CUX01 Pregunta 4</t>
         </is>
       </c>
       <c r="B936" s="5" t="n">
@@ -12625,7 +12625,7 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>CO08CUX07 Sobre las pistas</t>
+          <t>JU03CUX01 Conocer mis derechos</t>
         </is>
       </c>
       <c r="B937" s="5" t="n">
@@ -12638,7 +12638,7 @@
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>CO08CUX07 Cómo llego</t>
+          <t>JU02CUX01 Más información</t>
         </is>
       </c>
       <c r="B938" s="5" t="n">
@@ -12651,7 +12651,7 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>AM04CUX02 Qué hay para hacer</t>
+          <t>INN09CUX01 Cómo se genera</t>
         </is>
       </c>
       <c r="B939" s="5" t="n">
@@ -12664,7 +12664,7 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>AM04CUX02 Días y horarios</t>
+          <t>JU02CUX01 Hacer una consulta</t>
         </is>
       </c>
       <c r="B940" s="5" t="n">
@@ -12677,7 +12677,7 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>DH11CUX03 Responde bien MTV1</t>
+          <t>Hablar con operador</t>
         </is>
       </c>
       <c r="B941" s="5" t="n">
@@ -12690,7 +12690,7 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>DH11CUX03 Repaso MPV1</t>
+          <t>TUR01CUX03 Por lugar &gt; No sirve &gt; dirección verificada</t>
         </is>
       </c>
       <c r="B942" s="5" t="n">
@@ -12703,7 +12703,7 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>DH11CUX03  Apertura estático principal</t>
+          <t>GE02CUX02 Realidad histórica</t>
         </is>
       </c>
       <c r="B943" s="5" t="n">
@@ -12716,7 +12716,7 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>DH08CUX03  Apertura de contingencia III</t>
+          <t>TU03CUX13 Apertura</t>
         </is>
       </c>
       <c r="B944" s="5" t="n">
@@ -12729,7 +12729,7 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t xml:space="preserve">DH07CUX01 Cómo anotarme </t>
+          <t>EDU05CUX02 * Becas</t>
         </is>
       </c>
       <c r="B945" s="5" t="n">
@@ -12742,7 +12742,7 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>TUR01CUX03 Validación turno</t>
+          <t>Acciones previas a cada mensaje</t>
         </is>
       </c>
       <c r="B946" s="5" t="n">
@@ -12755,7 +12755,7 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>SAC05CUX01 En horario disponible</t>
+          <t xml:space="preserve">EDU04CUX30 Niñez </t>
         </is>
       </c>
       <c r="B947" s="5" t="n">
@@ -12768,7 +12768,7 @@
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>SA17CUX01 Sí – Está en el padrón</t>
+          <t>Test IABA Feedback</t>
         </is>
       </c>
       <c r="B948" s="5" t="n">
@@ -12781,7 +12781,7 @@
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>SA08CUX02 Quiero ser donante</t>
+          <t>TUR01CUX13 Ya tenía turno</t>
         </is>
       </c>
       <c r="B949" s="5" t="n">
@@ -12794,7 +12794,7 @@
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>Qué necesito | Fotocopia de Documentación Archivada</t>
+          <t>AM04CUX02 Qué hay para hacer</t>
         </is>
       </c>
       <c r="B950" s="5" t="n">
@@ -12807,7 +12807,7 @@
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>Qué necesito espectáculos musicales en vivo</t>
+          <t>AM04CUX03 Plantas y animales</t>
         </is>
       </c>
       <c r="B951" s="5" t="n">
@@ -12820,7 +12820,7 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>Qué necesito - Trámites Rúbrica</t>
+          <t>VI01CUX03 Validar datos</t>
         </is>
       </c>
       <c r="B952" s="5" t="n">
@@ -12833,7 +12833,7 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>Prueba disparador para cola de atencion</t>
+          <t>​​DH02CUX01 Requisitos​</t>
         </is>
       </c>
       <c r="B953" s="5" t="n">
@@ -12846,7 +12846,7 @@
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>PiaW Falla en el servicio de audio</t>
+          <t>AC05CUX01  Apertura</t>
         </is>
       </c>
       <c r="B954" s="5" t="n">
@@ -12859,7 +12859,7 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
-          <t>CU01CUX11 Apertura</t>
+          <t>📅 Sacar un turno</t>
         </is>
       </c>
       <c r="B955" s="5" t="n">
@@ -12870,145 +12870,15 @@
       </c>
     </row>
     <row r="956">
-      <c r="A956" t="inlineStr">
-        <is>
-          <t>CU01CUX07 Patio</t>
-        </is>
-      </c>
-      <c r="B956" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C956" s="6" t="n">
-        <v>4.788455608143439e-07</v>
-      </c>
-    </row>
-    <row r="957">
-      <c r="A957" t="inlineStr">
-        <is>
-          <t>CU01CUX07 Contracultura</t>
-        </is>
-      </c>
-      <c r="B957" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C957" s="6" t="n">
-        <v>4.788455608143439e-07</v>
-      </c>
-    </row>
-    <row r="958">
-      <c r="A958" t="inlineStr">
-        <is>
-          <t>SA01CUX01N Tips de prevención</t>
-        </is>
-      </c>
-      <c r="B958" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C958" s="6" t="n">
-        <v>4.788455608143439e-07</v>
-      </c>
-    </row>
-    <row r="959">
-      <c r="A959" t="inlineStr">
-        <is>
-          <t>Resolver Ubicación Domicilio | Fachada</t>
-        </is>
-      </c>
-      <c r="B959" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C959" s="6" t="n">
-        <v>4.788455608143439e-07</v>
-      </c>
-    </row>
-    <row r="960">
-      <c r="A960" t="inlineStr">
-        <is>
-          <t>¿En qué consiste el trámite de Modificación de Datos?</t>
-        </is>
-      </c>
-      <c r="B960" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C960" s="6" t="n">
-        <v>4.788455608143439e-07</v>
-      </c>
-    </row>
-    <row r="961">
-      <c r="A961" t="inlineStr">
-        <is>
-          <t>AC05CUX01  Apertura</t>
-        </is>
-      </c>
-      <c r="B961" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C961" s="6" t="n">
-        <v>4.788455608143439e-07</v>
-      </c>
-    </row>
-    <row r="962">
-      <c r="A962" t="inlineStr">
-        <is>
-          <t>fulfilled of Otro Tramite</t>
-        </is>
-      </c>
-      <c r="B962" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C962" s="6" t="n">
-        <v>4.788455608143439e-07</v>
-      </c>
-    </row>
-    <row r="963">
-      <c r="A963" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VI03CUX01 Cómo funciona </t>
-        </is>
-      </c>
-      <c r="B963" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C963" s="6" t="n">
-        <v>4.788455608143439e-07</v>
-      </c>
-    </row>
-    <row r="964">
-      <c r="A964" t="inlineStr">
-        <is>
-          <t>VI01CUX06 Bonificación</t>
-        </is>
-      </c>
-      <c r="B964" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C964" s="6" t="n">
-        <v>4.788455608143439e-07</v>
-      </c>
-    </row>
-    <row r="965">
-      <c r="A965" t="inlineStr">
-        <is>
-          <t>Test IABA Feedback</t>
-        </is>
-      </c>
-      <c r="B965" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C965" s="6" t="n">
-        <v>4.788455608143439e-07</v>
-      </c>
-    </row>
-    <row r="966">
-      <c r="A966" s="7" t="inlineStr">
+      <c r="A956" s="7" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B966" s="8" t="n">
+      <c r="B956" s="8" t="n">
         <v>2088356</v>
       </c>
-      <c r="C966" s="9" t="n">
+      <c r="C956" s="9" t="n">
         <v>1</v>
       </c>
     </row>
